--- a/Du_lieu_mau_GDPT2018_30lop.xlsx
+++ b/Du_lieu_mau_GDPT2018_30lop.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7241" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7245" uniqueCount="594">
   <si>
     <t>Hướng dẫn sử dụng workbook phân công giảng dạy GDPT 2018</t>
   </si>
@@ -1774,6 +1774,12 @@
   </si>
   <si>
     <t>Phòng máy thứ ba</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>Phòng thực hành Sinh học thứ hai</t>
   </si>
   <si>
     <t>Tổng hợp tải giảng dạy theo giáo viên - 2025-2026</t>
@@ -30810,7 +30816,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -31995,6 +32001,26 @@
       </c>
       <c r="G52" t="s">
         <v>583</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>584</v>
+      </c>
+      <c r="B53" t="s">
+        <v>553</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
+      </c>
+      <c r="D53">
+        <v>45</v>
+      </c>
+      <c r="E53" t="s">
+        <v>493</v>
+      </c>
+      <c r="G53" t="s">
+        <v>585</v>
       </c>
     </row>
   </sheetData>
@@ -32024,46 +32050,46 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="2" ht="22.35" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -32086,25 +32112,25 @@
         <v>102</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>40</v>

--- a/Du_lieu_mau_GDPT2018_30lop.xlsx
+++ b/Du_lieu_mau_GDPT2018_30lop.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7245" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7257" uniqueCount="595">
   <si>
     <t>Hướng dẫn sử dụng workbook phân công giảng dạy GDPT 2018</t>
   </si>
@@ -1804,6 +1804,9 @@
   </si>
   <si>
     <t>Số dòng PC HK2</t>
+  </si>
+  <si>
+    <t>Cột chênh đã trừ 10 tiết nghi lễ (chào cờ, sinh hoạt cuối tuần)</t>
   </si>
 </sst>
 </file>
@@ -1946,7 +1949,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1974,12 +1977,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -32034,7 +32031,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N76"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -32137,2844 +32134,3260 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3">
         <v>17</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3">
         <v>17</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3">
+        <v>12</v>
+      </c>
+      <c r="H3">
+        <v>12</v>
+      </c>
+      <c r="I3">
+        <v>-5</v>
+      </c>
+      <c r="J3">
+        <v>-5</v>
+      </c>
+      <c r="K3">
+        <v>24</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+      <c r="N3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4">
+        <v>17</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>17</v>
+      </c>
+      <c r="G4">
+        <v>12</v>
+      </c>
+      <c r="H4">
+        <v>12</v>
+      </c>
+      <c r="I4">
+        <v>-5</v>
+      </c>
+      <c r="J4">
+        <v>-5</v>
+      </c>
+      <c r="K4">
+        <v>24</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+      <c r="N4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>17</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>12</v>
+      </c>
+      <c r="I5">
+        <v>-5</v>
+      </c>
+      <c r="J5">
+        <v>-5</v>
+      </c>
+      <c r="K5">
+        <v>24</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+      <c r="N5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>17</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>-9</v>
+      </c>
+      <c r="J6">
+        <v>-9</v>
+      </c>
+      <c r="K6">
+        <v>16</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>17</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>-5</v>
+      </c>
+      <c r="J7">
+        <v>-5</v>
+      </c>
+      <c r="K7">
+        <v>24</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
+      <c r="N7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8">
+        <v>17</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>17</v>
+      </c>
+      <c r="G8">
+        <v>12</v>
+      </c>
+      <c r="H8">
+        <v>12</v>
+      </c>
+      <c r="I8">
+        <v>-5</v>
+      </c>
+      <c r="J8">
+        <v>-5</v>
+      </c>
+      <c r="K8">
+        <v>24</v>
+      </c>
+      <c r="L8">
+        <v>3</v>
+      </c>
+      <c r="M8">
+        <v>3</v>
+      </c>
+      <c r="N8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9">
+        <v>17</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>17</v>
+      </c>
+      <c r="G9">
+        <v>12</v>
+      </c>
+      <c r="H9">
+        <v>12</v>
+      </c>
+      <c r="I9">
+        <v>-5</v>
+      </c>
+      <c r="J9">
+        <v>-5</v>
+      </c>
+      <c r="K9">
+        <v>24</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>3</v>
+      </c>
+      <c r="N9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10">
+        <v>17</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>17</v>
+      </c>
+      <c r="G10">
+        <v>12</v>
+      </c>
+      <c r="H10">
+        <v>12</v>
+      </c>
+      <c r="I10">
+        <v>-5</v>
+      </c>
+      <c r="J10">
+        <v>-5</v>
+      </c>
+      <c r="K10">
+        <v>24</v>
+      </c>
+      <c r="L10">
+        <v>3</v>
+      </c>
+      <c r="M10">
+        <v>3</v>
+      </c>
+      <c r="N10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11">
+        <v>17</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>17</v>
+      </c>
+      <c r="G11">
+        <v>16</v>
+      </c>
+      <c r="H11">
+        <v>16</v>
+      </c>
+      <c r="I11">
+        <v>-1</v>
+      </c>
+      <c r="J11">
+        <v>-1</v>
+      </c>
+      <c r="K11">
+        <v>32</v>
+      </c>
+      <c r="L11">
+        <v>4</v>
+      </c>
+      <c r="M11">
+        <v>4</v>
+      </c>
+      <c r="N11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12">
+        <v>17</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>14</v>
+      </c>
+      <c r="G12">
+        <v>12</v>
+      </c>
+      <c r="H12">
+        <v>12</v>
+      </c>
+      <c r="I12">
+        <v>-2</v>
+      </c>
+      <c r="J12">
+        <v>-2</v>
+      </c>
+      <c r="K12">
+        <v>24</v>
+      </c>
+      <c r="L12">
+        <v>3</v>
+      </c>
+      <c r="M12">
+        <v>3</v>
+      </c>
+      <c r="N12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D13">
+        <v>17</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>17</v>
+      </c>
+      <c r="G13">
+        <v>12</v>
+      </c>
+      <c r="H13">
+        <v>12</v>
+      </c>
+      <c r="I13">
+        <v>-5</v>
+      </c>
+      <c r="J13">
+        <v>-5</v>
+      </c>
+      <c r="K13">
+        <v>24</v>
+      </c>
+      <c r="L13">
+        <v>4</v>
+      </c>
+      <c r="M13">
+        <v>4</v>
+      </c>
+      <c r="N13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D14">
+        <v>17</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>17</v>
+      </c>
+      <c r="G14">
+        <v>12</v>
+      </c>
+      <c r="H14">
+        <v>12</v>
+      </c>
+      <c r="I14">
+        <v>-5</v>
+      </c>
+      <c r="J14">
+        <v>-5</v>
+      </c>
+      <c r="K14">
+        <v>24</v>
+      </c>
+      <c r="L14">
+        <v>4</v>
+      </c>
+      <c r="M14">
+        <v>4</v>
+      </c>
+      <c r="N14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>155</v>
+      </c>
+      <c r="B15" t="s">
+        <v>156</v>
+      </c>
+      <c r="C15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D15">
+        <v>17</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>17</v>
+      </c>
+      <c r="G15">
+        <v>9</v>
+      </c>
+      <c r="H15">
+        <v>9</v>
+      </c>
+      <c r="I15">
+        <v>-8</v>
+      </c>
+      <c r="J15">
+        <v>-8</v>
+      </c>
+      <c r="K15">
+        <v>18</v>
+      </c>
+      <c r="L15">
+        <v>3</v>
+      </c>
+      <c r="M15">
+        <v>3</v>
+      </c>
+      <c r="N15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" t="s">
+        <v>160</v>
+      </c>
+      <c r="C16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D16">
+        <v>17</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>17</v>
+      </c>
+      <c r="G16">
+        <v>9</v>
+      </c>
+      <c r="H16">
+        <v>9</v>
+      </c>
+      <c r="I16">
+        <v>-8</v>
+      </c>
+      <c r="J16">
+        <v>-8</v>
+      </c>
+      <c r="K16">
+        <v>18</v>
+      </c>
+      <c r="L16">
+        <v>3</v>
+      </c>
+      <c r="M16">
+        <v>3</v>
+      </c>
+      <c r="N16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>163</v>
+      </c>
+      <c r="B17" t="s">
+        <v>164</v>
+      </c>
+      <c r="C17" t="s">
+        <v>150</v>
+      </c>
+      <c r="D17">
+        <v>17</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>17</v>
+      </c>
+      <c r="G17">
+        <v>12</v>
+      </c>
+      <c r="H17">
+        <v>12</v>
+      </c>
+      <c r="I17">
+        <v>-5</v>
+      </c>
+      <c r="J17">
+        <v>-5</v>
+      </c>
+      <c r="K17">
+        <v>24</v>
+      </c>
+      <c r="L17">
+        <v>4</v>
+      </c>
+      <c r="M17">
+        <v>4</v>
+      </c>
+      <c r="N17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C18" t="s">
+        <v>150</v>
+      </c>
+      <c r="D18">
+        <v>17</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>17</v>
+      </c>
+      <c r="G18">
+        <v>12</v>
+      </c>
+      <c r="H18">
+        <v>12</v>
+      </c>
+      <c r="I18">
+        <v>-5</v>
+      </c>
+      <c r="J18">
+        <v>-5</v>
+      </c>
+      <c r="K18">
+        <v>24</v>
+      </c>
+      <c r="L18">
+        <v>4</v>
+      </c>
+      <c r="M18">
+        <v>4</v>
+      </c>
+      <c r="N18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>171</v>
+      </c>
+      <c r="B19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C19" t="s">
+        <v>150</v>
+      </c>
+      <c r="D19">
+        <v>17</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>17</v>
+      </c>
+      <c r="G19">
+        <v>15</v>
+      </c>
+      <c r="H19">
+        <v>15</v>
+      </c>
+      <c r="I19">
+        <v>-2</v>
+      </c>
+      <c r="J19">
+        <v>-2</v>
+      </c>
+      <c r="K19">
+        <v>30</v>
+      </c>
+      <c r="L19">
+        <v>5</v>
+      </c>
+      <c r="M19">
+        <v>5</v>
+      </c>
+      <c r="N19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>175</v>
+      </c>
+      <c r="B20" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" t="s">
+        <v>150</v>
+      </c>
+      <c r="D20">
+        <v>17</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20">
+        <v>14</v>
+      </c>
+      <c r="G20">
+        <v>9</v>
+      </c>
+      <c r="H20">
+        <v>9</v>
+      </c>
+      <c r="I20">
+        <v>-5</v>
+      </c>
+      <c r="J20">
+        <v>-5</v>
+      </c>
+      <c r="K20">
+        <v>18</v>
+      </c>
+      <c r="L20">
+        <v>3</v>
+      </c>
+      <c r="M20">
+        <v>3</v>
+      </c>
+      <c r="N20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B21" t="s">
+        <v>181</v>
+      </c>
+      <c r="C21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D21">
+        <v>17</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>17</v>
+      </c>
+      <c r="G21">
+        <v>12</v>
+      </c>
+      <c r="H21">
+        <v>12</v>
+      </c>
+      <c r="I21">
+        <v>-5</v>
+      </c>
+      <c r="J21">
+        <v>-5</v>
+      </c>
+      <c r="K21">
+        <v>24</v>
+      </c>
+      <c r="L21">
+        <v>4</v>
+      </c>
+      <c r="M21">
+        <v>4</v>
+      </c>
+      <c r="N21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>185</v>
+      </c>
+      <c r="B22" t="s">
+        <v>186</v>
+      </c>
+      <c r="C22" t="s">
+        <v>184</v>
+      </c>
+      <c r="D22">
+        <v>17</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>17</v>
+      </c>
+      <c r="G22">
+        <v>12</v>
+      </c>
+      <c r="H22">
+        <v>12</v>
+      </c>
+      <c r="I22">
+        <v>-5</v>
+      </c>
+      <c r="J22">
+        <v>-5</v>
+      </c>
+      <c r="K22">
+        <v>24</v>
+      </c>
+      <c r="L22">
+        <v>4</v>
+      </c>
+      <c r="M22">
+        <v>4</v>
+      </c>
+      <c r="N22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>189</v>
+      </c>
+      <c r="B23" t="s">
+        <v>190</v>
+      </c>
+      <c r="C23" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23">
+        <v>17</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>17</v>
+      </c>
+      <c r="G23">
+        <v>9</v>
+      </c>
+      <c r="H23">
+        <v>9</v>
+      </c>
+      <c r="I23">
+        <v>-8</v>
+      </c>
+      <c r="J23">
+        <v>-8</v>
+      </c>
+      <c r="K23">
+        <v>18</v>
+      </c>
+      <c r="L23">
+        <v>3</v>
+      </c>
+      <c r="M23">
+        <v>3</v>
+      </c>
+      <c r="N23" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" t="s">
+        <v>194</v>
+      </c>
+      <c r="C24" t="s">
+        <v>184</v>
+      </c>
+      <c r="D24">
+        <v>17</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>17</v>
+      </c>
+      <c r="G24">
+        <v>9</v>
+      </c>
+      <c r="H24">
+        <v>9</v>
+      </c>
+      <c r="I24">
+        <v>-8</v>
+      </c>
+      <c r="J24">
+        <v>-8</v>
+      </c>
+      <c r="K24">
+        <v>18</v>
+      </c>
+      <c r="L24">
+        <v>3</v>
+      </c>
+      <c r="M24">
+        <v>3</v>
+      </c>
+      <c r="N24" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>197</v>
+      </c>
+      <c r="B25" t="s">
+        <v>198</v>
+      </c>
+      <c r="C25" t="s">
+        <v>184</v>
+      </c>
+      <c r="D25">
+        <v>17</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>17</v>
+      </c>
+      <c r="G25">
+        <v>12</v>
+      </c>
+      <c r="H25">
+        <v>12</v>
+      </c>
+      <c r="I25">
+        <v>-5</v>
+      </c>
+      <c r="J25">
+        <v>-5</v>
+      </c>
+      <c r="K25">
+        <v>24</v>
+      </c>
+      <c r="L25">
+        <v>4</v>
+      </c>
+      <c r="M25">
+        <v>4</v>
+      </c>
+      <c r="N25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>201</v>
+      </c>
+      <c r="B26" t="s">
+        <v>202</v>
+      </c>
+      <c r="C26" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26">
+        <v>17</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>17</v>
+      </c>
+      <c r="G26">
+        <v>12</v>
+      </c>
+      <c r="H26">
+        <v>12</v>
+      </c>
+      <c r="I26">
+        <v>-5</v>
+      </c>
+      <c r="J26">
+        <v>-5</v>
+      </c>
+      <c r="K26">
+        <v>24</v>
+      </c>
+      <c r="L26">
+        <v>4</v>
+      </c>
+      <c r="M26">
+        <v>4</v>
+      </c>
+      <c r="N26" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>205</v>
+      </c>
+      <c r="B27" t="s">
+        <v>206</v>
+      </c>
+      <c r="C27" t="s">
+        <v>184</v>
+      </c>
+      <c r="D27">
+        <v>17</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>17</v>
+      </c>
+      <c r="G27">
+        <v>15</v>
+      </c>
+      <c r="H27">
+        <v>15</v>
+      </c>
+      <c r="I27">
+        <v>-2</v>
+      </c>
+      <c r="J27">
+        <v>-2</v>
+      </c>
+      <c r="K27">
+        <v>30</v>
+      </c>
+      <c r="L27">
+        <v>5</v>
+      </c>
+      <c r="M27">
+        <v>5</v>
+      </c>
+      <c r="N27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>209</v>
+      </c>
+      <c r="B28" t="s">
+        <v>210</v>
+      </c>
+      <c r="C28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28">
+        <v>17</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+      <c r="F28">
+        <v>14</v>
+      </c>
+      <c r="G28">
+        <v>9</v>
+      </c>
+      <c r="H28">
+        <v>9</v>
+      </c>
+      <c r="I28">
+        <v>-5</v>
+      </c>
+      <c r="J28">
+        <v>-5</v>
+      </c>
+      <c r="K28">
+        <v>18</v>
+      </c>
+      <c r="L28">
+        <v>3</v>
+      </c>
+      <c r="M28">
+        <v>3</v>
+      </c>
+      <c r="N28" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>214</v>
+      </c>
+      <c r="B29" t="s">
+        <v>215</v>
+      </c>
+      <c r="C29" t="s">
+        <v>218</v>
+      </c>
+      <c r="D29">
+        <v>17</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>17</v>
+      </c>
+      <c r="G29">
+        <v>14</v>
+      </c>
+      <c r="H29">
+        <v>14</v>
+      </c>
+      <c r="I29">
+        <v>-3</v>
+      </c>
+      <c r="J29">
+        <v>-3</v>
+      </c>
+      <c r="K29">
+        <v>28</v>
+      </c>
+      <c r="L29">
+        <v>9</v>
+      </c>
+      <c r="M29">
+        <v>9</v>
+      </c>
+      <c r="N29" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>219</v>
+      </c>
+      <c r="B30" t="s">
+        <v>220</v>
+      </c>
+      <c r="C30" t="s">
+        <v>218</v>
+      </c>
+      <c r="D30">
+        <v>17</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>17</v>
+      </c>
+      <c r="G30">
+        <v>13</v>
+      </c>
+      <c r="H30">
+        <v>13</v>
+      </c>
+      <c r="I30">
+        <v>-4</v>
+      </c>
+      <c r="J30">
+        <v>-4</v>
+      </c>
+      <c r="K30">
+        <v>26</v>
+      </c>
+      <c r="L30">
+        <v>8</v>
+      </c>
+      <c r="M30">
+        <v>8</v>
+      </c>
+      <c r="N30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>223</v>
+      </c>
+      <c r="B31" t="s">
+        <v>224</v>
+      </c>
+      <c r="C31" t="s">
+        <v>218</v>
+      </c>
+      <c r="D31">
+        <v>17</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>17</v>
+      </c>
+      <c r="G31">
+        <v>13</v>
+      </c>
+      <c r="H31">
+        <v>13</v>
+      </c>
+      <c r="I31">
+        <v>-4</v>
+      </c>
+      <c r="J31">
+        <v>-4</v>
+      </c>
+      <c r="K31">
+        <v>26</v>
+      </c>
+      <c r="L31">
+        <v>9</v>
+      </c>
+      <c r="M31">
+        <v>9</v>
+      </c>
+      <c r="N31" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>227</v>
+      </c>
+      <c r="B32" t="s">
+        <v>228</v>
+      </c>
+      <c r="C32" t="s">
+        <v>218</v>
+      </c>
+      <c r="D32">
+        <v>17</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>17</v>
+      </c>
+      <c r="G32">
+        <v>13</v>
+      </c>
+      <c r="H32">
+        <v>13</v>
+      </c>
+      <c r="I32">
+        <v>-4</v>
+      </c>
+      <c r="J32">
+        <v>-4</v>
+      </c>
+      <c r="K32">
+        <v>26</v>
+      </c>
+      <c r="L32">
+        <v>9</v>
+      </c>
+      <c r="M32">
+        <v>9</v>
+      </c>
+      <c r="N32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>231</v>
+      </c>
+      <c r="B33" t="s">
+        <v>232</v>
+      </c>
+      <c r="C33" t="s">
+        <v>218</v>
+      </c>
+      <c r="D33">
+        <v>17</v>
+      </c>
+      <c r="E33">
+        <v>3</v>
+      </c>
+      <c r="F33">
+        <v>14</v>
+      </c>
+      <c r="G33">
+        <v>13</v>
+      </c>
+      <c r="H33">
+        <v>13</v>
+      </c>
+      <c r="I33">
+        <v>-1</v>
+      </c>
+      <c r="J33">
+        <v>-1</v>
+      </c>
+      <c r="K33">
+        <v>26</v>
+      </c>
+      <c r="L33">
+        <v>9</v>
+      </c>
+      <c r="M33">
+        <v>9</v>
+      </c>
+      <c r="N33" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>236</v>
+      </c>
+      <c r="B34" t="s">
+        <v>237</v>
+      </c>
+      <c r="C34" t="s">
+        <v>240</v>
+      </c>
+      <c r="D34">
+        <v>17</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>17</v>
+      </c>
+      <c r="G34">
+        <v>14</v>
+      </c>
+      <c r="H34">
+        <v>14</v>
+      </c>
+      <c r="I34">
+        <v>-3</v>
+      </c>
+      <c r="J34">
+        <v>-3</v>
+      </c>
+      <c r="K34">
+        <v>28</v>
+      </c>
+      <c r="L34">
+        <v>9</v>
+      </c>
+      <c r="M34">
+        <v>9</v>
+      </c>
+      <c r="N34" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>241</v>
+      </c>
+      <c r="B35" t="s">
+        <v>242</v>
+      </c>
+      <c r="C35" t="s">
+        <v>240</v>
+      </c>
+      <c r="D35">
+        <v>17</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>17</v>
+      </c>
+      <c r="G35">
+        <v>13</v>
+      </c>
+      <c r="H35">
+        <v>13</v>
+      </c>
+      <c r="I35">
+        <v>-4</v>
+      </c>
+      <c r="J35">
+        <v>-4</v>
+      </c>
+      <c r="K35">
+        <v>26</v>
+      </c>
+      <c r="L35">
+        <v>8</v>
+      </c>
+      <c r="M35">
+        <v>8</v>
+      </c>
+      <c r="N35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>245</v>
+      </c>
+      <c r="B36" t="s">
+        <v>246</v>
+      </c>
+      <c r="C36" t="s">
+        <v>240</v>
+      </c>
+      <c r="D36">
+        <v>17</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>17</v>
+      </c>
+      <c r="G36">
+        <v>13</v>
+      </c>
+      <c r="H36">
+        <v>13</v>
+      </c>
+      <c r="I36">
+        <v>-4</v>
+      </c>
+      <c r="J36">
+        <v>-4</v>
+      </c>
+      <c r="K36">
+        <v>26</v>
+      </c>
+      <c r="L36">
+        <v>9</v>
+      </c>
+      <c r="M36">
+        <v>9</v>
+      </c>
+      <c r="N36" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>249</v>
+      </c>
+      <c r="B37" t="s">
+        <v>250</v>
+      </c>
+      <c r="C37" t="s">
+        <v>240</v>
+      </c>
+      <c r="D37">
+        <v>17</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>17</v>
+      </c>
+      <c r="G37">
+        <v>13</v>
+      </c>
+      <c r="H37">
+        <v>13</v>
+      </c>
+      <c r="I37">
+        <v>-4</v>
+      </c>
+      <c r="J37">
+        <v>-4</v>
+      </c>
+      <c r="K37">
+        <v>26</v>
+      </c>
+      <c r="L37">
+        <v>9</v>
+      </c>
+      <c r="M37">
+        <v>9</v>
+      </c>
+      <c r="N37" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>253</v>
+      </c>
+      <c r="B38" t="s">
+        <v>254</v>
+      </c>
+      <c r="C38" t="s">
+        <v>240</v>
+      </c>
+      <c r="D38">
+        <v>17</v>
+      </c>
+      <c r="E38">
+        <v>3</v>
+      </c>
+      <c r="F38">
+        <v>14</v>
+      </c>
+      <c r="G38">
+        <v>13</v>
+      </c>
+      <c r="H38">
+        <v>13</v>
+      </c>
+      <c r="I38">
+        <v>-1</v>
+      </c>
+      <c r="J38">
+        <v>-1</v>
+      </c>
+      <c r="K38">
+        <v>26</v>
+      </c>
+      <c r="L38">
+        <v>9</v>
+      </c>
+      <c r="M38">
+        <v>9</v>
+      </c>
+      <c r="N38" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>258</v>
+      </c>
+      <c r="B39" t="s">
+        <v>259</v>
+      </c>
+      <c r="C39" t="s">
+        <v>261</v>
+      </c>
+      <c r="D39">
+        <v>17</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>17</v>
+      </c>
+      <c r="G39">
+        <v>15</v>
+      </c>
+      <c r="H39">
+        <v>15</v>
+      </c>
+      <c r="I39">
+        <v>-2</v>
+      </c>
+      <c r="J39">
+        <v>-2</v>
+      </c>
+      <c r="K39">
+        <v>30</v>
+      </c>
+      <c r="L39">
+        <v>10</v>
+      </c>
+      <c r="M39">
+        <v>10</v>
+      </c>
+      <c r="N39" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>262</v>
+      </c>
+      <c r="B40" t="s">
+        <v>263</v>
+      </c>
+      <c r="C40" t="s">
+        <v>261</v>
+      </c>
+      <c r="D40">
+        <v>17</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>17</v>
+      </c>
+      <c r="G40">
+        <v>15</v>
+      </c>
+      <c r="H40">
+        <v>15</v>
+      </c>
+      <c r="I40">
+        <v>-2</v>
+      </c>
+      <c r="J40">
+        <v>-2</v>
+      </c>
+      <c r="K40">
+        <v>30</v>
+      </c>
+      <c r="L40">
+        <v>10</v>
+      </c>
+      <c r="M40">
+        <v>10</v>
+      </c>
+      <c r="N40" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>266</v>
+      </c>
+      <c r="B41" t="s">
+        <v>267</v>
+      </c>
+      <c r="C41" t="s">
+        <v>261</v>
+      </c>
+      <c r="D41">
+        <v>17</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>17</v>
+      </c>
+      <c r="G41">
+        <v>15</v>
+      </c>
+      <c r="H41">
+        <v>15</v>
+      </c>
+      <c r="I41">
+        <v>-2</v>
+      </c>
+      <c r="J41">
+        <v>-2</v>
+      </c>
+      <c r="K41">
+        <v>30</v>
+      </c>
+      <c r="L41">
+        <v>10</v>
+      </c>
+      <c r="M41">
+        <v>10</v>
+      </c>
+      <c r="N41" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>270</v>
+      </c>
+      <c r="B42" t="s">
+        <v>271</v>
+      </c>
+      <c r="C42" t="s">
+        <v>273</v>
+      </c>
+      <c r="D42">
+        <v>17</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>17</v>
+      </c>
+      <c r="G42">
+        <v>12</v>
+      </c>
+      <c r="H42">
+        <v>12</v>
+      </c>
+      <c r="I42">
+        <v>-5</v>
+      </c>
+      <c r="J42">
+        <v>-5</v>
+      </c>
+      <c r="K42">
+        <v>24</v>
+      </c>
+      <c r="L42">
+        <v>6</v>
+      </c>
+      <c r="M42">
+        <v>6</v>
+      </c>
+      <c r="N42" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>274</v>
+      </c>
+      <c r="B43" t="s">
+        <v>275</v>
+      </c>
+      <c r="C43" t="s">
+        <v>273</v>
+      </c>
+      <c r="D43">
+        <v>17</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>17</v>
+      </c>
+      <c r="G43">
+        <v>12</v>
+      </c>
+      <c r="H43">
+        <v>12</v>
+      </c>
+      <c r="I43">
+        <v>-5</v>
+      </c>
+      <c r="J43">
+        <v>-5</v>
+      </c>
+      <c r="K43">
+        <v>24</v>
+      </c>
+      <c r="L43">
+        <v>6</v>
+      </c>
+      <c r="M43">
+        <v>6</v>
+      </c>
+      <c r="N43" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>277</v>
+      </c>
+      <c r="B44" t="s">
+        <v>278</v>
+      </c>
+      <c r="C44" t="s">
+        <v>273</v>
+      </c>
+      <c r="D44">
+        <v>17</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>17</v>
+      </c>
+      <c r="G44">
+        <v>12</v>
+      </c>
+      <c r="H44">
+        <v>12</v>
+      </c>
+      <c r="I44">
+        <v>-5</v>
+      </c>
+      <c r="J44">
+        <v>-5</v>
+      </c>
+      <c r="K44">
+        <v>24</v>
+      </c>
+      <c r="L44">
+        <v>6</v>
+      </c>
+      <c r="M44">
+        <v>6</v>
+      </c>
+      <c r="N44" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>281</v>
+      </c>
+      <c r="B45" t="s">
+        <v>282</v>
+      </c>
+      <c r="C45" t="s">
+        <v>273</v>
+      </c>
+      <c r="D45">
+        <v>17</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>17</v>
+      </c>
+      <c r="G45">
+        <v>12</v>
+      </c>
+      <c r="H45">
+        <v>12</v>
+      </c>
+      <c r="I45">
+        <v>-5</v>
+      </c>
+      <c r="J45">
+        <v>-5</v>
+      </c>
+      <c r="K45">
+        <v>24</v>
+      </c>
+      <c r="L45">
+        <v>6</v>
+      </c>
+      <c r="M45">
+        <v>6</v>
+      </c>
+      <c r="N45" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>284</v>
+      </c>
+      <c r="B46" t="s">
+        <v>285</v>
+      </c>
+      <c r="C46" t="s">
+        <v>273</v>
+      </c>
+      <c r="D46">
+        <v>17</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>17</v>
+      </c>
+      <c r="G46">
+        <v>12</v>
+      </c>
+      <c r="H46">
+        <v>12</v>
+      </c>
+      <c r="I46">
+        <v>-5</v>
+      </c>
+      <c r="J46">
+        <v>-5</v>
+      </c>
+      <c r="K46">
+        <v>24</v>
+      </c>
+      <c r="L46">
+        <v>6</v>
+      </c>
+      <c r="M46">
+        <v>6</v>
+      </c>
+      <c r="N46" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>287</v>
+      </c>
+      <c r="B47" t="s">
+        <v>288</v>
+      </c>
+      <c r="C47" t="s">
+        <v>291</v>
+      </c>
+      <c r="D47">
+        <v>17</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>17</v>
+      </c>
+      <c r="G47">
+        <v>9</v>
+      </c>
+      <c r="H47">
+        <v>9</v>
+      </c>
+      <c r="I47">
+        <v>-8</v>
+      </c>
+      <c r="J47">
+        <v>-8</v>
+      </c>
+      <c r="K47">
+        <v>18</v>
+      </c>
+      <c r="L47">
+        <v>3</v>
+      </c>
+      <c r="M47">
+        <v>3</v>
+      </c>
+      <c r="N47" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>292</v>
+      </c>
+      <c r="B48" t="s">
+        <v>293</v>
+      </c>
+      <c r="C48" t="s">
+        <v>291</v>
+      </c>
+      <c r="D48">
+        <v>17</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>17</v>
+      </c>
+      <c r="G48">
+        <v>9</v>
+      </c>
+      <c r="H48">
+        <v>9</v>
+      </c>
+      <c r="I48">
+        <v>-8</v>
+      </c>
+      <c r="J48">
+        <v>-8</v>
+      </c>
+      <c r="K48">
+        <v>18</v>
+      </c>
+      <c r="L48">
+        <v>3</v>
+      </c>
+      <c r="M48">
+        <v>3</v>
+      </c>
+      <c r="N48" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>296</v>
+      </c>
+      <c r="B49" t="s">
+        <v>297</v>
+      </c>
+      <c r="C49" t="s">
+        <v>291</v>
+      </c>
+      <c r="D49">
+        <v>17</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>17</v>
+      </c>
+      <c r="G49">
+        <v>8</v>
+      </c>
+      <c r="H49">
+        <v>8</v>
+      </c>
+      <c r="I49">
+        <v>-9</v>
+      </c>
+      <c r="J49">
+        <v>-9</v>
+      </c>
+      <c r="K49">
+        <v>16</v>
+      </c>
+      <c r="L49">
+        <v>3</v>
+      </c>
+      <c r="M49">
+        <v>3</v>
+      </c>
+      <c r="N49" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>300</v>
+      </c>
+      <c r="B50" t="s">
+        <v>301</v>
+      </c>
+      <c r="C50" t="s">
+        <v>303</v>
+      </c>
+      <c r="D50">
+        <v>17</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>17</v>
+      </c>
+      <c r="G50">
+        <v>12</v>
+      </c>
+      <c r="H50">
+        <v>12</v>
+      </c>
+      <c r="I50">
+        <v>-5</v>
+      </c>
+      <c r="J50">
+        <v>-5</v>
+      </c>
+      <c r="K50">
+        <v>24</v>
+      </c>
+      <c r="L50">
+        <v>4</v>
+      </c>
+      <c r="M50">
+        <v>4</v>
+      </c>
+      <c r="N50" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>304</v>
+      </c>
+      <c r="B51" t="s">
+        <v>305</v>
+      </c>
+      <c r="C51" t="s">
+        <v>303</v>
+      </c>
+      <c r="D51">
+        <v>17</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>17</v>
+      </c>
+      <c r="G51">
+        <v>12</v>
+      </c>
+      <c r="H51">
+        <v>12</v>
+      </c>
+      <c r="I51">
+        <v>-5</v>
+      </c>
+      <c r="J51">
+        <v>-5</v>
+      </c>
+      <c r="K51">
+        <v>24</v>
+      </c>
+      <c r="L51">
+        <v>4</v>
+      </c>
+      <c r="M51">
+        <v>4</v>
+      </c>
+      <c r="N51" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>307</v>
+      </c>
+      <c r="B52" t="s">
+        <v>308</v>
+      </c>
+      <c r="C52" t="s">
+        <v>310</v>
+      </c>
+      <c r="D52">
+        <v>17</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>17</v>
+      </c>
+      <c r="G52">
+        <v>14</v>
+      </c>
+      <c r="H52">
+        <v>14</v>
+      </c>
+      <c r="I52">
+        <v>-3</v>
+      </c>
+      <c r="J52">
+        <v>-3</v>
+      </c>
+      <c r="K52">
+        <v>28</v>
+      </c>
+      <c r="L52">
+        <v>11</v>
+      </c>
+      <c r="M52">
+        <v>11</v>
+      </c>
+      <c r="N52" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>311</v>
+      </c>
+      <c r="B53" t="s">
+        <v>312</v>
+      </c>
+      <c r="C53" t="s">
+        <v>310</v>
+      </c>
+      <c r="D53">
+        <v>17</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>17</v>
+      </c>
+      <c r="G53">
+        <v>14</v>
+      </c>
+      <c r="H53">
+        <v>14</v>
+      </c>
+      <c r="I53">
+        <v>-3</v>
+      </c>
+      <c r="J53">
+        <v>-3</v>
+      </c>
+      <c r="K53">
+        <v>28</v>
+      </c>
+      <c r="L53">
+        <v>11</v>
+      </c>
+      <c r="M53">
+        <v>11</v>
+      </c>
+      <c r="N53" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>314</v>
+      </c>
+      <c r="B54" t="s">
+        <v>315</v>
+      </c>
+      <c r="C54" t="s">
+        <v>310</v>
+      </c>
+      <c r="D54">
+        <v>17</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>17</v>
+      </c>
+      <c r="G54">
+        <v>14</v>
+      </c>
+      <c r="H54">
+        <v>14</v>
+      </c>
+      <c r="I54">
+        <v>-3</v>
+      </c>
+      <c r="J54">
+        <v>-3</v>
+      </c>
+      <c r="K54">
+        <v>28</v>
+      </c>
+      <c r="L54">
+        <v>11</v>
+      </c>
+      <c r="M54">
+        <v>11</v>
+      </c>
+      <c r="N54" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>317</v>
+      </c>
+      <c r="B55" t="s">
+        <v>318</v>
+      </c>
+      <c r="C55" t="s">
+        <v>310</v>
+      </c>
+      <c r="D55">
+        <v>17</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>17</v>
+      </c>
+      <c r="G55">
+        <v>14</v>
+      </c>
+      <c r="H55">
+        <v>14</v>
+      </c>
+      <c r="I55">
+        <v>-3</v>
+      </c>
+      <c r="J55">
+        <v>-3</v>
+      </c>
+      <c r="K55">
+        <v>28</v>
+      </c>
+      <c r="L55">
+        <v>11</v>
+      </c>
+      <c r="M55">
+        <v>11</v>
+      </c>
+      <c r="N55" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>320</v>
+      </c>
+      <c r="B56" t="s">
+        <v>321</v>
+      </c>
+      <c r="C56" t="s">
+        <v>323</v>
+      </c>
+      <c r="D56">
+        <v>17</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>17</v>
+      </c>
+      <c r="G56">
+        <v>10</v>
+      </c>
+      <c r="H56">
+        <v>10</v>
+      </c>
+      <c r="I56">
+        <v>-7</v>
+      </c>
+      <c r="J56">
+        <v>-7</v>
+      </c>
+      <c r="K56">
         <v>20</v>
       </c>
-      <c r="H3" s="3">
+      <c r="L56">
+        <v>5</v>
+      </c>
+      <c r="M56">
+        <v>5</v>
+      </c>
+      <c r="N56" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>324</v>
+      </c>
+      <c r="B57" t="s">
+        <v>325</v>
+      </c>
+      <c r="C57" t="s">
+        <v>323</v>
+      </c>
+      <c r="D57">
+        <v>17</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>17</v>
+      </c>
+      <c r="G57">
+        <v>10</v>
+      </c>
+      <c r="H57">
+        <v>10</v>
+      </c>
+      <c r="I57">
+        <v>-7</v>
+      </c>
+      <c r="J57">
+        <v>-7</v>
+      </c>
+      <c r="K57">
         <v>20</v>
       </c>
-      <c r="I3" s="3">
-        <v>3</v>
-      </c>
-      <c r="J3" s="3">
-        <v>3</v>
-      </c>
-      <c r="K3" s="3">
+      <c r="L57">
         <v>5</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="M57">
+        <v>5</v>
+      </c>
+      <c r="N57" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>327</v>
+      </c>
+      <c r="B58" t="s">
+        <v>328</v>
+      </c>
+      <c r="C58" t="s">
+        <v>323</v>
+      </c>
+      <c r="D58">
         <v>17</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E58">
         <v>0</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F58">
         <v>17</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G58">
+        <v>10</v>
+      </c>
+      <c r="H58">
+        <v>10</v>
+      </c>
+      <c r="I58">
+        <v>-7</v>
+      </c>
+      <c r="J58">
+        <v>-7</v>
+      </c>
+      <c r="K58">
         <v>20</v>
       </c>
-      <c r="H4" s="4">
+      <c r="L58">
+        <v>5</v>
+      </c>
+      <c r="M58">
+        <v>5</v>
+      </c>
+      <c r="N58" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>330</v>
+      </c>
+      <c r="B59" t="s">
+        <v>331</v>
+      </c>
+      <c r="C59" t="s">
+        <v>333</v>
+      </c>
+      <c r="D59">
+        <v>17</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>17</v>
+      </c>
+      <c r="G59">
+        <v>4</v>
+      </c>
+      <c r="H59">
+        <v>4</v>
+      </c>
+      <c r="I59">
+        <v>-13</v>
+      </c>
+      <c r="J59">
+        <v>-13</v>
+      </c>
+      <c r="K59">
+        <v>8</v>
+      </c>
+      <c r="L59">
+        <v>2</v>
+      </c>
+      <c r="M59">
+        <v>2</v>
+      </c>
+      <c r="N59" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>334</v>
+      </c>
+      <c r="B60" t="s">
+        <v>335</v>
+      </c>
+      <c r="C60" t="s">
+        <v>337</v>
+      </c>
+      <c r="D60">
+        <v>17</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>17</v>
+      </c>
+      <c r="G60">
+        <v>12</v>
+      </c>
+      <c r="H60">
+        <v>12</v>
+      </c>
+      <c r="I60">
+        <v>-5</v>
+      </c>
+      <c r="J60">
+        <v>-5</v>
+      </c>
+      <c r="K60">
+        <v>24</v>
+      </c>
+      <c r="L60">
+        <v>6</v>
+      </c>
+      <c r="M60">
+        <v>6</v>
+      </c>
+      <c r="N60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>338</v>
+      </c>
+      <c r="B61" t="s">
+        <v>339</v>
+      </c>
+      <c r="C61" t="s">
+        <v>337</v>
+      </c>
+      <c r="D61">
+        <v>17</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>17</v>
+      </c>
+      <c r="G61">
+        <v>12</v>
+      </c>
+      <c r="H61">
+        <v>12</v>
+      </c>
+      <c r="I61">
+        <v>-5</v>
+      </c>
+      <c r="J61">
+        <v>-5</v>
+      </c>
+      <c r="K61">
+        <v>24</v>
+      </c>
+      <c r="L61">
+        <v>6</v>
+      </c>
+      <c r="M61">
+        <v>6</v>
+      </c>
+      <c r="N61" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>341</v>
+      </c>
+      <c r="B62" t="s">
+        <v>342</v>
+      </c>
+      <c r="C62" t="s">
+        <v>337</v>
+      </c>
+      <c r="D62">
+        <v>17</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>17</v>
+      </c>
+      <c r="G62">
+        <v>12</v>
+      </c>
+      <c r="H62">
+        <v>12</v>
+      </c>
+      <c r="I62">
+        <v>-5</v>
+      </c>
+      <c r="J62">
+        <v>-5</v>
+      </c>
+      <c r="K62">
+        <v>24</v>
+      </c>
+      <c r="L62">
+        <v>6</v>
+      </c>
+      <c r="M62">
+        <v>6</v>
+      </c>
+      <c r="N62" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>344</v>
+      </c>
+      <c r="B63" t="s">
+        <v>345</v>
+      </c>
+      <c r="C63" t="s">
+        <v>337</v>
+      </c>
+      <c r="D63">
+        <v>17</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>17</v>
+      </c>
+      <c r="G63">
+        <v>12</v>
+      </c>
+      <c r="H63">
+        <v>12</v>
+      </c>
+      <c r="I63">
+        <v>-5</v>
+      </c>
+      <c r="J63">
+        <v>-5</v>
+      </c>
+      <c r="K63">
+        <v>24</v>
+      </c>
+      <c r="L63">
+        <v>6</v>
+      </c>
+      <c r="M63">
+        <v>6</v>
+      </c>
+      <c r="N63" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>347</v>
+      </c>
+      <c r="B64" t="s">
+        <v>348</v>
+      </c>
+      <c r="C64" t="s">
+        <v>337</v>
+      </c>
+      <c r="D64">
+        <v>17</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>17</v>
+      </c>
+      <c r="G64">
+        <v>12</v>
+      </c>
+      <c r="H64">
+        <v>12</v>
+      </c>
+      <c r="I64">
+        <v>-5</v>
+      </c>
+      <c r="J64">
+        <v>-5</v>
+      </c>
+      <c r="K64">
+        <v>24</v>
+      </c>
+      <c r="L64">
+        <v>6</v>
+      </c>
+      <c r="M64">
+        <v>6</v>
+      </c>
+      <c r="N64" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>350</v>
+      </c>
+      <c r="B65" t="s">
+        <v>351</v>
+      </c>
+      <c r="C65" t="s">
+        <v>353</v>
+      </c>
+      <c r="D65">
+        <v>17</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>17</v>
+      </c>
+      <c r="G65">
+        <v>10</v>
+      </c>
+      <c r="H65">
+        <v>10</v>
+      </c>
+      <c r="I65">
+        <v>-7</v>
+      </c>
+      <c r="J65">
+        <v>-7</v>
+      </c>
+      <c r="K65">
         <v>20</v>
       </c>
-      <c r="I4" s="4">
-        <v>3</v>
-      </c>
-      <c r="J4" s="4">
-        <v>3</v>
-      </c>
-      <c r="K4" s="4">
-        <v>5</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" s="3">
+      <c r="L65">
+        <v>10</v>
+      </c>
+      <c r="M65">
+        <v>10</v>
+      </c>
+      <c r="N65" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>354</v>
+      </c>
+      <c r="B66" t="s">
+        <v>355</v>
+      </c>
+      <c r="C66" t="s">
+        <v>353</v>
+      </c>
+      <c r="D66">
         <v>17</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E66">
         <v>0</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F66">
         <v>17</v>
       </c>
-      <c r="G5" s="3">
-        <v>16</v>
-      </c>
-      <c r="H5" s="3">
-        <v>16</v>
-      </c>
-      <c r="I5" s="3">
-        <v>-1</v>
-      </c>
-      <c r="J5" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K5" s="3">
-        <v>4</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="G66">
+        <v>10</v>
+      </c>
+      <c r="H66">
+        <v>10</v>
+      </c>
+      <c r="I66">
+        <v>-7</v>
+      </c>
+      <c r="J66">
+        <v>-7</v>
+      </c>
+      <c r="K66">
+        <v>20</v>
+      </c>
+      <c r="L66">
+        <v>10</v>
+      </c>
+      <c r="M66">
+        <v>10</v>
+      </c>
+      <c r="N66" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>357</v>
+      </c>
+      <c r="B67" t="s">
+        <v>358</v>
+      </c>
+      <c r="C67" t="s">
+        <v>353</v>
+      </c>
+      <c r="D67">
         <v>17</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E67">
         <v>0</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F67">
         <v>17</v>
       </c>
-      <c r="G6" s="4">
-        <v>16</v>
-      </c>
-      <c r="H6" s="4">
-        <v>16</v>
-      </c>
-      <c r="I6" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J6" s="4">
-        <v>-1</v>
-      </c>
-      <c r="K6" s="4">
-        <v>4</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D7" s="3">
+      <c r="G67">
+        <v>10</v>
+      </c>
+      <c r="H67">
+        <v>10</v>
+      </c>
+      <c r="I67">
+        <v>-7</v>
+      </c>
+      <c r="J67">
+        <v>-7</v>
+      </c>
+      <c r="K67">
+        <v>20</v>
+      </c>
+      <c r="L67">
+        <v>10</v>
+      </c>
+      <c r="M67">
+        <v>10</v>
+      </c>
+      <c r="N67" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>360</v>
+      </c>
+      <c r="B68" t="s">
+        <v>361</v>
+      </c>
+      <c r="C68" t="s">
+        <v>363</v>
+      </c>
+      <c r="D68">
         <v>17</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E68">
         <v>0</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F68">
         <v>17</v>
       </c>
-      <c r="G7" s="3">
-        <v>16</v>
-      </c>
-      <c r="H7" s="3">
-        <v>16</v>
-      </c>
-      <c r="I7" s="3">
-        <v>-1</v>
-      </c>
-      <c r="J7" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K7" s="3">
-        <v>4</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="G68">
+        <v>25</v>
+      </c>
+      <c r="H68">
+        <v>25</v>
+      </c>
+      <c r="I68">
+        <v>-2</v>
+      </c>
+      <c r="J68">
+        <v>-2</v>
+      </c>
+      <c r="K68">
+        <v>50</v>
+      </c>
+      <c r="L68">
         <v>17</v>
       </c>
-      <c r="E8" s="4">
+      <c r="M68">
+        <v>17</v>
+      </c>
+      <c r="N68" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>364</v>
+      </c>
+      <c r="B69" t="s">
+        <v>365</v>
+      </c>
+      <c r="C69" t="s">
+        <v>363</v>
+      </c>
+      <c r="D69">
+        <v>17</v>
+      </c>
+      <c r="E69">
         <v>0</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F69">
         <v>17</v>
       </c>
-      <c r="G8" s="4">
-        <v>16</v>
-      </c>
-      <c r="H8" s="4">
-        <v>16</v>
-      </c>
-      <c r="I8" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J8" s="4">
-        <v>-1</v>
-      </c>
-      <c r="K8" s="4">
-        <v>4</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D9" s="3">
+      <c r="G69">
+        <v>25</v>
+      </c>
+      <c r="H69">
+        <v>25</v>
+      </c>
+      <c r="I69">
+        <v>-2</v>
+      </c>
+      <c r="J69">
+        <v>-2</v>
+      </c>
+      <c r="K69">
+        <v>50</v>
+      </c>
+      <c r="L69">
         <v>17</v>
       </c>
-      <c r="E9" s="3">
+      <c r="M69">
+        <v>17</v>
+      </c>
+      <c r="N69" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>367</v>
+      </c>
+      <c r="B70" t="s">
+        <v>368</v>
+      </c>
+      <c r="C70" t="s">
+        <v>363</v>
+      </c>
+      <c r="D70">
+        <v>17</v>
+      </c>
+      <c r="E70">
         <v>0</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F70">
         <v>17</v>
       </c>
-      <c r="G9" s="3">
-        <v>16</v>
-      </c>
-      <c r="H9" s="3">
-        <v>16</v>
-      </c>
-      <c r="I9" s="3">
-        <v>-1</v>
-      </c>
-      <c r="J9" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K9" s="3">
-        <v>4</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="G70">
+        <v>25</v>
+      </c>
+      <c r="H70">
+        <v>25</v>
+      </c>
+      <c r="I70">
+        <v>-2</v>
+      </c>
+      <c r="J70">
+        <v>-2</v>
+      </c>
+      <c r="K70">
+        <v>50</v>
+      </c>
+      <c r="L70">
         <v>17</v>
       </c>
-      <c r="E10" s="4">
+      <c r="M70">
+        <v>17</v>
+      </c>
+      <c r="N70" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>370</v>
+      </c>
+      <c r="B71" t="s">
+        <v>371</v>
+      </c>
+      <c r="C71" t="s">
+        <v>363</v>
+      </c>
+      <c r="D71">
+        <v>17</v>
+      </c>
+      <c r="E71">
         <v>0</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F71">
         <v>17</v>
       </c>
-      <c r="G10" s="4">
-        <v>16</v>
-      </c>
-      <c r="H10" s="4">
-        <v>16</v>
-      </c>
-      <c r="I10" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J10" s="4">
-        <v>-1</v>
-      </c>
-      <c r="K10" s="4">
-        <v>4</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="G71">
+        <v>25</v>
+      </c>
+      <c r="H71">
+        <v>25</v>
+      </c>
+      <c r="I71">
+        <v>-2</v>
+      </c>
+      <c r="J71">
+        <v>-2</v>
+      </c>
+      <c r="K71">
+        <v>50</v>
+      </c>
+      <c r="L71">
         <v>17</v>
       </c>
-      <c r="E11" s="3">
+      <c r="M71">
+        <v>17</v>
+      </c>
+      <c r="N71" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>373</v>
+      </c>
+      <c r="B72" t="s">
+        <v>374</v>
+      </c>
+      <c r="C72" t="s">
+        <v>363</v>
+      </c>
+      <c r="D72">
+        <v>17</v>
+      </c>
+      <c r="E72">
         <v>0</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F72">
         <v>17</v>
       </c>
-      <c r="G11" s="3">
-        <v>16</v>
-      </c>
-      <c r="H11" s="3">
-        <v>16</v>
-      </c>
-      <c r="I11" s="3">
-        <v>-1</v>
-      </c>
-      <c r="J11" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K11" s="3">
-        <v>4</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="G72">
+        <v>25</v>
+      </c>
+      <c r="H72">
+        <v>25</v>
+      </c>
+      <c r="I72">
+        <v>-2</v>
+      </c>
+      <c r="J72">
+        <v>-2</v>
+      </c>
+      <c r="K72">
+        <v>50</v>
+      </c>
+      <c r="L72">
         <v>17</v>
       </c>
-      <c r="E12" s="4">
-        <v>3</v>
-      </c>
-      <c r="F12" s="4">
-        <v>14</v>
-      </c>
-      <c r="G12" s="4">
-        <v>16</v>
-      </c>
-      <c r="H12" s="4">
-        <v>16</v>
-      </c>
-      <c r="I12" s="4">
-        <v>2</v>
-      </c>
-      <c r="J12" s="4">
-        <v>2</v>
-      </c>
-      <c r="K12" s="4">
-        <v>4</v>
-      </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D13" s="3">
+      <c r="M72">
         <v>17</v>
       </c>
-      <c r="E13" s="3">
+      <c r="N72" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>376</v>
+      </c>
+      <c r="B73" t="s">
+        <v>377</v>
+      </c>
+      <c r="C73" t="s">
+        <v>363</v>
+      </c>
+      <c r="D73">
+        <v>17</v>
+      </c>
+      <c r="E73">
         <v>0</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F73">
         <v>17</v>
       </c>
-      <c r="G13" s="3">
-        <v>18</v>
-      </c>
-      <c r="H13" s="3">
-        <v>18</v>
-      </c>
-      <c r="I13" s="3">
-        <v>1</v>
-      </c>
-      <c r="J13" s="3">
-        <v>1</v>
-      </c>
-      <c r="K13" s="3">
-        <v>6</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D14" s="4">
+      <c r="G73">
+        <v>25</v>
+      </c>
+      <c r="H73">
+        <v>25</v>
+      </c>
+      <c r="I73">
+        <v>-2</v>
+      </c>
+      <c r="J73">
+        <v>-2</v>
+      </c>
+      <c r="K73">
+        <v>50</v>
+      </c>
+      <c r="L73">
         <v>17</v>
       </c>
-      <c r="E14" s="4">
+      <c r="M73">
+        <v>17</v>
+      </c>
+      <c r="N73" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>379</v>
+      </c>
+      <c r="B74" t="s">
+        <v>380</v>
+      </c>
+      <c r="C74" t="s">
+        <v>363</v>
+      </c>
+      <c r="D74">
+        <v>17</v>
+      </c>
+      <c r="E74">
         <v>0</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F74">
         <v>17</v>
       </c>
-      <c r="G14" s="4">
-        <v>18</v>
-      </c>
-      <c r="H14" s="4">
-        <v>18</v>
-      </c>
-      <c r="I14" s="4">
-        <v>1</v>
-      </c>
-      <c r="J14" s="4">
-        <v>1</v>
-      </c>
-      <c r="K14" s="4">
-        <v>6</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D15" s="3">
+      <c r="G74">
+        <v>15</v>
+      </c>
+      <c r="H74">
+        <v>15</v>
+      </c>
+      <c r="I74">
+        <v>-2</v>
+      </c>
+      <c r="J74">
+        <v>-2</v>
+      </c>
+      <c r="K74">
+        <v>30</v>
+      </c>
+      <c r="L74">
+        <v>9</v>
+      </c>
+      <c r="M74">
+        <v>9</v>
+      </c>
+      <c r="N74" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>382</v>
+      </c>
+      <c r="B75" t="s">
+        <v>383</v>
+      </c>
+      <c r="C75" t="s">
+        <v>363</v>
+      </c>
+      <c r="D75">
         <v>17</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E75">
         <v>0</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F75">
         <v>17</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G75">
         <v>15</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H75">
         <v>15</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I75">
         <v>-2</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J75">
         <v>-2</v>
       </c>
-      <c r="K15" s="3">
-        <v>5</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D16" s="4">
+      <c r="K75">
+        <v>30</v>
+      </c>
+      <c r="L75">
+        <v>9</v>
+      </c>
+      <c r="M75">
+        <v>9</v>
+      </c>
+      <c r="N75" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>385</v>
+      </c>
+      <c r="B76" t="s">
+        <v>386</v>
+      </c>
+      <c r="C76" t="s">
+        <v>310</v>
+      </c>
+      <c r="D76">
         <v>17</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E76">
         <v>0</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F76">
         <v>17</v>
       </c>
-      <c r="G16" s="4">
-        <v>15</v>
-      </c>
-      <c r="H16" s="4">
-        <v>15</v>
-      </c>
-      <c r="I16" s="4">
-        <v>-2</v>
-      </c>
-      <c r="J16" s="4">
-        <v>-2</v>
-      </c>
-      <c r="K16" s="4">
-        <v>5</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D17" s="3">
-        <v>17</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>17</v>
-      </c>
-      <c r="G17" s="3">
-        <v>15</v>
-      </c>
-      <c r="H17" s="3">
-        <v>15</v>
-      </c>
-      <c r="I17" s="3">
-        <v>-2</v>
-      </c>
-      <c r="J17" s="3">
-        <v>-2</v>
-      </c>
-      <c r="K17" s="3">
-        <v>5</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D18" s="4">
-        <v>17</v>
-      </c>
-      <c r="E18" s="4">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4">
-        <v>17</v>
-      </c>
-      <c r="G18" s="4">
-        <v>15</v>
-      </c>
-      <c r="H18" s="4">
-        <v>15</v>
-      </c>
-      <c r="I18" s="4">
-        <v>-2</v>
-      </c>
-      <c r="J18" s="4">
-        <v>-2</v>
-      </c>
-      <c r="K18" s="4">
-        <v>5</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D19" s="3">
-        <v>17</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3">
-        <v>17</v>
-      </c>
-      <c r="G19" s="3">
-        <v>15</v>
-      </c>
-      <c r="H19" s="3">
-        <v>15</v>
-      </c>
-      <c r="I19" s="3">
-        <v>-2</v>
-      </c>
-      <c r="J19" s="3">
-        <v>-2</v>
-      </c>
-      <c r="K19" s="3">
-        <v>5</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D20" s="4">
-        <v>17</v>
-      </c>
-      <c r="E20" s="4">
-        <v>3</v>
-      </c>
-      <c r="F20" s="4">
-        <v>14</v>
-      </c>
-      <c r="G20" s="4">
-        <v>15</v>
-      </c>
-      <c r="H20" s="4">
-        <v>15</v>
-      </c>
-      <c r="I20" s="4">
-        <v>1</v>
-      </c>
-      <c r="J20" s="4">
-        <v>1</v>
-      </c>
-      <c r="K20" s="4">
-        <v>5</v>
-      </c>
-      <c r="L20" s="4"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D21" s="3">
-        <v>17</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
-        <v>17</v>
-      </c>
-      <c r="G21" s="3">
-        <v>18</v>
-      </c>
-      <c r="H21" s="3">
-        <v>18</v>
-      </c>
-      <c r="I21" s="3">
-        <v>1</v>
-      </c>
-      <c r="J21" s="3">
-        <v>1</v>
-      </c>
-      <c r="K21" s="3">
-        <v>6</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D22" s="4">
-        <v>17</v>
-      </c>
-      <c r="E22" s="4">
-        <v>0</v>
-      </c>
-      <c r="F22" s="4">
-        <v>17</v>
-      </c>
-      <c r="G22" s="4">
-        <v>18</v>
-      </c>
-      <c r="H22" s="4">
-        <v>18</v>
-      </c>
-      <c r="I22" s="4">
-        <v>1</v>
-      </c>
-      <c r="J22" s="4">
-        <v>1</v>
-      </c>
-      <c r="K22" s="4">
-        <v>6</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D23" s="3">
-        <v>17</v>
-      </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3">
-        <v>17</v>
-      </c>
-      <c r="G23" s="3">
-        <v>15</v>
-      </c>
-      <c r="H23" s="3">
-        <v>15</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-2</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-2</v>
-      </c>
-      <c r="K23" s="3">
-        <v>5</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D24" s="4">
-        <v>17</v>
-      </c>
-      <c r="E24" s="4">
-        <v>0</v>
-      </c>
-      <c r="F24" s="4">
-        <v>17</v>
-      </c>
-      <c r="G24" s="4">
-        <v>15</v>
-      </c>
-      <c r="H24" s="4">
-        <v>15</v>
-      </c>
-      <c r="I24" s="4">
-        <v>-2</v>
-      </c>
-      <c r="J24" s="4">
-        <v>-2</v>
-      </c>
-      <c r="K24" s="4">
-        <v>5</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D25" s="3">
-        <v>17</v>
-      </c>
-      <c r="E25" s="3">
-        <v>0</v>
-      </c>
-      <c r="F25" s="3">
-        <v>17</v>
-      </c>
-      <c r="G25" s="3">
-        <v>15</v>
-      </c>
-      <c r="H25" s="3">
-        <v>15</v>
-      </c>
-      <c r="I25" s="3">
-        <v>-2</v>
-      </c>
-      <c r="J25" s="3">
-        <v>-2</v>
-      </c>
-      <c r="K25" s="3">
-        <v>5</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D26" s="4">
-        <v>17</v>
-      </c>
-      <c r="E26" s="4">
-        <v>0</v>
-      </c>
-      <c r="F26" s="4">
-        <v>17</v>
-      </c>
-      <c r="G26" s="4">
-        <v>15</v>
-      </c>
-      <c r="H26" s="4">
-        <v>15</v>
-      </c>
-      <c r="I26" s="4">
-        <v>-2</v>
-      </c>
-      <c r="J26" s="4">
-        <v>-2</v>
-      </c>
-      <c r="K26" s="4">
-        <v>5</v>
-      </c>
-      <c r="L26" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D27" s="3">
-        <v>17</v>
-      </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3">
-        <v>17</v>
-      </c>
-      <c r="G27" s="3">
-        <v>15</v>
-      </c>
-      <c r="H27" s="3">
-        <v>15</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-2</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-2</v>
-      </c>
-      <c r="K27" s="3">
-        <v>5</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D28" s="4">
-        <v>17</v>
-      </c>
-      <c r="E28" s="4">
-        <v>3</v>
-      </c>
-      <c r="F28" s="4">
-        <v>14</v>
-      </c>
-      <c r="G28" s="4">
-        <v>15</v>
-      </c>
-      <c r="H28" s="4">
-        <v>15</v>
-      </c>
-      <c r="I28" s="4">
-        <v>1</v>
-      </c>
-      <c r="J28" s="4">
-        <v>1</v>
-      </c>
-      <c r="K28" s="4">
-        <v>5</v>
-      </c>
-      <c r="L28" s="4"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D29" s="3">
-        <v>17</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>17</v>
-      </c>
-      <c r="G29" s="3">
-        <v>18</v>
-      </c>
-      <c r="H29" s="3">
-        <v>18</v>
-      </c>
-      <c r="I29" s="3">
-        <v>1</v>
-      </c>
-      <c r="J29" s="3">
-        <v>1</v>
-      </c>
-      <c r="K29" s="3">
-        <v>18</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="D30" s="4">
-        <v>17</v>
-      </c>
-      <c r="E30" s="4">
-        <v>0</v>
-      </c>
-      <c r="F30" s="4">
-        <v>17</v>
-      </c>
-      <c r="G30" s="4">
-        <v>18</v>
-      </c>
-      <c r="H30" s="4">
-        <v>18</v>
-      </c>
-      <c r="I30" s="4">
-        <v>1</v>
-      </c>
-      <c r="J30" s="4">
-        <v>1</v>
-      </c>
-      <c r="K30" s="4">
-        <v>18</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D31" s="3">
-        <v>17</v>
-      </c>
-      <c r="E31" s="3">
-        <v>0</v>
-      </c>
-      <c r="F31" s="3">
-        <v>17</v>
-      </c>
-      <c r="G31" s="3">
-        <v>18</v>
-      </c>
-      <c r="H31" s="3">
-        <v>18</v>
-      </c>
-      <c r="I31" s="3">
-        <v>1</v>
-      </c>
-      <c r="J31" s="3">
-        <v>1</v>
-      </c>
-      <c r="K31" s="3">
-        <v>18</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="D32" s="4">
-        <v>17</v>
-      </c>
-      <c r="E32" s="4">
-        <v>0</v>
-      </c>
-      <c r="F32" s="4">
-        <v>17</v>
-      </c>
-      <c r="G32" s="4">
-        <v>18</v>
-      </c>
-      <c r="H32" s="4">
-        <v>18</v>
-      </c>
-      <c r="I32" s="4">
-        <v>1</v>
-      </c>
-      <c r="J32" s="4">
-        <v>1</v>
-      </c>
-      <c r="K32" s="4">
-        <v>18</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D33" s="3">
-        <v>17</v>
-      </c>
-      <c r="E33" s="3">
-        <v>3</v>
-      </c>
-      <c r="F33" s="3">
-        <v>14</v>
-      </c>
-      <c r="G33" s="3">
-        <v>18</v>
-      </c>
-      <c r="H33" s="3">
-        <v>18</v>
-      </c>
-      <c r="I33" s="3">
-        <v>4</v>
-      </c>
-      <c r="J33" s="3">
-        <v>4</v>
-      </c>
-      <c r="K33" s="3">
-        <v>18</v>
-      </c>
-      <c r="L33" s="3"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="D34" s="4">
-        <v>17</v>
-      </c>
-      <c r="E34" s="4">
-        <v>0</v>
-      </c>
-      <c r="F34" s="4">
-        <v>17</v>
-      </c>
-      <c r="G34" s="4">
-        <v>18</v>
-      </c>
-      <c r="H34" s="4">
-        <v>18</v>
-      </c>
-      <c r="I34" s="4">
-        <v>1</v>
-      </c>
-      <c r="J34" s="4">
-        <v>1</v>
-      </c>
-      <c r="K34" s="4">
-        <v>18</v>
-      </c>
-      <c r="L34" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D35" s="3">
-        <v>17</v>
-      </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3">
-        <v>17</v>
-      </c>
-      <c r="G35" s="3">
-        <v>18</v>
-      </c>
-      <c r="H35" s="3">
-        <v>18</v>
-      </c>
-      <c r="I35" s="3">
-        <v>1</v>
-      </c>
-      <c r="J35" s="3">
-        <v>1</v>
-      </c>
-      <c r="K35" s="3">
-        <v>18</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="D36" s="4">
-        <v>17</v>
-      </c>
-      <c r="E36" s="4">
-        <v>0</v>
-      </c>
-      <c r="F36" s="4">
-        <v>17</v>
-      </c>
-      <c r="G36" s="4">
-        <v>18</v>
-      </c>
-      <c r="H36" s="4">
-        <v>18</v>
-      </c>
-      <c r="I36" s="4">
-        <v>1</v>
-      </c>
-      <c r="J36" s="4">
-        <v>1</v>
-      </c>
-      <c r="K36" s="4">
-        <v>18</v>
-      </c>
-      <c r="L36" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D37" s="3">
-        <v>17</v>
-      </c>
-      <c r="E37" s="3">
-        <v>0</v>
-      </c>
-      <c r="F37" s="3">
-        <v>17</v>
-      </c>
-      <c r="G37" s="3">
-        <v>18</v>
-      </c>
-      <c r="H37" s="3">
-        <v>18</v>
-      </c>
-      <c r="I37" s="3">
-        <v>1</v>
-      </c>
-      <c r="J37" s="3">
-        <v>1</v>
-      </c>
-      <c r="K37" s="3">
-        <v>18</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="D38" s="4">
-        <v>17</v>
-      </c>
-      <c r="E38" s="4">
-        <v>3</v>
-      </c>
-      <c r="F38" s="4">
-        <v>14</v>
-      </c>
-      <c r="G38" s="4">
-        <v>18</v>
-      </c>
-      <c r="H38" s="4">
-        <v>18</v>
-      </c>
-      <c r="I38" s="4">
-        <v>4</v>
-      </c>
-      <c r="J38" s="4">
-        <v>4</v>
-      </c>
-      <c r="K38" s="4">
-        <v>18</v>
-      </c>
-      <c r="L38" s="4"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="D39" s="3">
-        <v>17</v>
-      </c>
-      <c r="E39" s="3">
-        <v>0</v>
-      </c>
-      <c r="F39" s="3">
-        <v>17</v>
-      </c>
-      <c r="G39" s="3">
-        <v>21</v>
-      </c>
-      <c r="H39" s="3">
-        <v>21</v>
-      </c>
-      <c r="I39" s="3">
-        <v>4</v>
-      </c>
-      <c r="J39" s="3">
-        <v>4</v>
-      </c>
-      <c r="K39" s="3">
-        <v>21</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="D40" s="4">
-        <v>17</v>
-      </c>
-      <c r="E40" s="4">
-        <v>0</v>
-      </c>
-      <c r="F40" s="4">
-        <v>17</v>
-      </c>
-      <c r="G40" s="4">
-        <v>21</v>
-      </c>
-      <c r="H40" s="4">
-        <v>21</v>
-      </c>
-      <c r="I40" s="4">
-        <v>4</v>
-      </c>
-      <c r="J40" s="4">
-        <v>4</v>
-      </c>
-      <c r="K40" s="4">
-        <v>21</v>
-      </c>
-      <c r="L40" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M40" s="11"/>
-      <c r="N40" s="11"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="D41" s="3">
-        <v>17</v>
-      </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
-      <c r="F41" s="3">
-        <v>17</v>
-      </c>
-      <c r="G41" s="3">
-        <v>21</v>
-      </c>
-      <c r="H41" s="3">
-        <v>21</v>
-      </c>
-      <c r="I41" s="3">
-        <v>4</v>
-      </c>
-      <c r="J41" s="3">
-        <v>4</v>
-      </c>
-      <c r="K41" s="3">
-        <v>21</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M41" s="10"/>
-      <c r="N41" s="10"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="D42" s="4">
-        <v>17</v>
-      </c>
-      <c r="E42" s="4">
-        <v>0</v>
-      </c>
-      <c r="F42" s="4">
-        <v>17</v>
-      </c>
-      <c r="G42" s="4">
-        <v>18</v>
-      </c>
-      <c r="H42" s="4">
-        <v>18</v>
-      </c>
-      <c r="I42" s="4">
-        <v>1</v>
-      </c>
-      <c r="J42" s="4">
-        <v>1</v>
-      </c>
-      <c r="K42" s="4">
-        <v>9</v>
-      </c>
-      <c r="L42" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M42" s="11"/>
-      <c r="N42" s="11"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="D43" s="3">
-        <v>17</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>17</v>
-      </c>
-      <c r="G43" s="3">
-        <v>18</v>
-      </c>
-      <c r="H43" s="3">
-        <v>18</v>
-      </c>
-      <c r="I43" s="3">
-        <v>1</v>
-      </c>
-      <c r="J43" s="3">
-        <v>1</v>
-      </c>
-      <c r="K43" s="3">
-        <v>9</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M43" s="10"/>
-      <c r="N43" s="10"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="D44" s="4">
-        <v>17</v>
-      </c>
-      <c r="E44" s="4">
-        <v>0</v>
-      </c>
-      <c r="F44" s="4">
-        <v>17</v>
-      </c>
-      <c r="G44" s="4">
-        <v>16</v>
-      </c>
-      <c r="H44" s="4">
-        <v>16</v>
-      </c>
-      <c r="I44" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J44" s="4">
-        <v>-1</v>
-      </c>
-      <c r="K44" s="4">
-        <v>8</v>
-      </c>
-      <c r="L44" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M44" s="11"/>
-      <c r="N44" s="11"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="D45" s="3">
-        <v>17</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>17</v>
-      </c>
-      <c r="G45" s="3">
-        <v>16</v>
-      </c>
-      <c r="H45" s="3">
-        <v>16</v>
-      </c>
-      <c r="I45" s="3">
-        <v>-1</v>
-      </c>
-      <c r="J45" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K45" s="3">
-        <v>8</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M45" s="10"/>
-      <c r="N45" s="10"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="D46" s="4">
-        <v>17</v>
-      </c>
-      <c r="E46" s="4">
-        <v>0</v>
-      </c>
-      <c r="F46" s="4">
-        <v>17</v>
-      </c>
-      <c r="G46" s="4">
-        <v>16</v>
-      </c>
-      <c r="H46" s="4">
-        <v>16</v>
-      </c>
-      <c r="I46" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J46" s="4">
-        <v>-1</v>
-      </c>
-      <c r="K46" s="4">
-        <v>8</v>
-      </c>
-      <c r="L46" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M46" s="11"/>
-      <c r="N46" s="11"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D47" s="3">
-        <v>17</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>17</v>
-      </c>
-      <c r="G47" s="3">
-        <v>16</v>
-      </c>
-      <c r="H47" s="3">
-        <v>16</v>
-      </c>
-      <c r="I47" s="3">
-        <v>-1</v>
-      </c>
-      <c r="J47" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="G76">
+        <v>13</v>
+      </c>
+      <c r="H76">
+        <v>13</v>
+      </c>
+      <c r="I76">
+        <v>-4</v>
+      </c>
+      <c r="J76">
+        <v>-4</v>
+      </c>
+      <c r="K76">
+        <v>26</v>
+      </c>
+      <c r="L76">
         <v>10</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M47" s="10"/>
-      <c r="N47" s="10"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="D48" s="4">
-        <v>17</v>
-      </c>
-      <c r="E48" s="4">
-        <v>0</v>
-      </c>
-      <c r="F48" s="4">
-        <v>17</v>
-      </c>
-      <c r="G48" s="4">
-        <v>16</v>
-      </c>
-      <c r="H48" s="4">
-        <v>16</v>
-      </c>
-      <c r="I48" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J48" s="4">
-        <v>-1</v>
-      </c>
-      <c r="K48" s="4">
+      <c r="M76">
         <v>10</v>
       </c>
-      <c r="L48" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M48" s="11"/>
-      <c r="N48" s="11"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D49" s="3">
-        <v>17</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>17</v>
-      </c>
-      <c r="G49" s="3">
-        <v>16</v>
-      </c>
-      <c r="H49" s="3">
-        <v>16</v>
-      </c>
-      <c r="I49" s="3">
-        <v>-1</v>
-      </c>
-      <c r="J49" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K49" s="3">
-        <v>10</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M49" s="10"/>
-      <c r="N49" s="10"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="D50" s="4">
-        <v>17</v>
-      </c>
-      <c r="E50" s="4">
-        <v>0</v>
-      </c>
-      <c r="F50" s="4">
-        <v>17</v>
-      </c>
-      <c r="G50" s="4">
-        <v>19</v>
-      </c>
-      <c r="H50" s="4">
-        <v>19</v>
-      </c>
-      <c r="I50" s="4">
-        <v>2</v>
-      </c>
-      <c r="J50" s="4">
-        <v>2</v>
-      </c>
-      <c r="K50" s="4">
-        <v>11</v>
-      </c>
-      <c r="L50" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M50" s="11"/>
-      <c r="N50" s="11"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="D51" s="3">
-        <v>17</v>
-      </c>
-      <c r="E51" s="3">
-        <v>0</v>
-      </c>
-      <c r="F51" s="3">
-        <v>17</v>
-      </c>
-      <c r="G51" s="3">
-        <v>14</v>
-      </c>
-      <c r="H51" s="3">
-        <v>14</v>
-      </c>
-      <c r="I51" s="3">
-        <v>-3</v>
-      </c>
-      <c r="J51" s="3">
-        <v>-3</v>
-      </c>
-      <c r="K51" s="3">
-        <v>10</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M51" s="10"/>
-      <c r="N51" s="10"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="D52" s="4">
-        <v>17</v>
-      </c>
-      <c r="E52" s="4">
-        <v>0</v>
-      </c>
-      <c r="F52" s="4">
-        <v>17</v>
-      </c>
-      <c r="G52" s="4">
-        <v>30</v>
-      </c>
-      <c r="H52" s="4">
-        <v>30</v>
-      </c>
-      <c r="I52" s="11">
-        <v>13</v>
-      </c>
-      <c r="J52" s="11">
-        <v>13</v>
-      </c>
-      <c r="K52" s="4">
-        <v>30</v>
-      </c>
-      <c r="L52" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M52" s="11"/>
-      <c r="N52" s="11"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="D53" s="3">
-        <v>17</v>
-      </c>
-      <c r="E53" s="3">
-        <v>0</v>
-      </c>
-      <c r="F53" s="3">
-        <v>17</v>
-      </c>
-      <c r="G53" s="3">
-        <v>18</v>
-      </c>
-      <c r="H53" s="3">
-        <v>18</v>
-      </c>
-      <c r="I53" s="3">
-        <v>1</v>
-      </c>
-      <c r="J53" s="3">
-        <v>1</v>
-      </c>
-      <c r="K53" s="3">
-        <v>18</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M53" s="10"/>
-      <c r="N53" s="10"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="D54" s="4">
-        <v>17</v>
-      </c>
-      <c r="E54" s="4">
-        <v>0</v>
-      </c>
-      <c r="F54" s="4">
-        <v>17</v>
-      </c>
-      <c r="G54" s="4">
-        <v>30</v>
-      </c>
-      <c r="H54" s="4">
-        <v>30</v>
-      </c>
-      <c r="I54" s="11">
-        <v>13</v>
-      </c>
-      <c r="J54" s="11">
-        <v>13</v>
-      </c>
-      <c r="K54" s="4">
-        <v>30</v>
-      </c>
-      <c r="L54" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M54" s="11"/>
-      <c r="N54" s="11"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="D55" s="3">
-        <v>17</v>
-      </c>
-      <c r="E55" s="3">
-        <v>0</v>
-      </c>
-      <c r="F55" s="3">
-        <v>17</v>
-      </c>
-      <c r="G55" s="3">
-        <v>18</v>
-      </c>
-      <c r="H55" s="3">
-        <v>18</v>
-      </c>
-      <c r="I55" s="3">
-        <v>1</v>
-      </c>
-      <c r="J55" s="3">
-        <v>1</v>
-      </c>
-      <c r="K55" s="3">
-        <v>18</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M55" s="10"/>
-      <c r="N55" s="10"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="D56" s="4">
-        <v>17</v>
-      </c>
-      <c r="E56" s="4">
-        <v>0</v>
-      </c>
-      <c r="F56" s="4">
-        <v>17</v>
-      </c>
-      <c r="G56" s="4">
-        <v>10</v>
-      </c>
-      <c r="H56" s="4">
-        <v>10</v>
-      </c>
-      <c r="I56" s="4">
-        <v>-7</v>
-      </c>
-      <c r="J56" s="4">
-        <v>-7</v>
-      </c>
-      <c r="K56" s="4">
-        <v>5</v>
-      </c>
-      <c r="L56" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M56" s="11"/>
-      <c r="N56" s="11"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D57" s="3">
-        <v>17</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>17</v>
-      </c>
-      <c r="G57" s="3">
-        <v>10</v>
-      </c>
-      <c r="H57" s="3">
-        <v>10</v>
-      </c>
-      <c r="I57" s="3">
-        <v>-7</v>
-      </c>
-      <c r="J57" s="3">
-        <v>-7</v>
-      </c>
-      <c r="K57" s="3">
-        <v>5</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M57" s="10"/>
-      <c r="N57" s="10"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="D58" s="4">
-        <v>17</v>
-      </c>
-      <c r="E58" s="4">
-        <v>0</v>
-      </c>
-      <c r="F58" s="4">
-        <v>17</v>
-      </c>
-      <c r="G58" s="4">
-        <v>10</v>
-      </c>
-      <c r="H58" s="4">
-        <v>10</v>
-      </c>
-      <c r="I58" s="4">
-        <v>-7</v>
-      </c>
-      <c r="J58" s="4">
-        <v>-7</v>
-      </c>
-      <c r="K58" s="4">
-        <v>5</v>
-      </c>
-      <c r="L58" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M58" s="11"/>
-      <c r="N58" s="11"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="D59" s="3">
-        <v>17</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>17</v>
-      </c>
-      <c r="G59" s="3">
-        <v>6</v>
-      </c>
-      <c r="H59" s="3">
-        <v>6</v>
-      </c>
-      <c r="I59" s="3">
-        <v>-11</v>
-      </c>
-      <c r="J59" s="3">
-        <v>-11</v>
-      </c>
-      <c r="K59" s="3">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M59" s="10"/>
-      <c r="N59" s="10"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D60" s="3">
-        <v>17</v>
-      </c>
-      <c r="E60" s="3">
-        <v>0</v>
-      </c>
-      <c r="F60" s="3">
-        <v>17</v>
-      </c>
-      <c r="G60" s="3">
-        <v>18</v>
-      </c>
-      <c r="H60" s="3">
-        <v>18</v>
-      </c>
-      <c r="I60" s="3">
-        <v>1</v>
-      </c>
-      <c r="J60" s="3">
-        <v>1</v>
-      </c>
-      <c r="K60" s="3">
-        <v>9</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M60" s="10"/>
-      <c r="N60" s="10"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="D61" s="4">
-        <v>17</v>
-      </c>
-      <c r="E61" s="4">
-        <v>0</v>
-      </c>
-      <c r="F61" s="4">
-        <v>17</v>
-      </c>
-      <c r="G61" s="4">
-        <v>18</v>
-      </c>
-      <c r="H61" s="4">
-        <v>18</v>
-      </c>
-      <c r="I61" s="4">
-        <v>1</v>
-      </c>
-      <c r="J61" s="4">
-        <v>1</v>
-      </c>
-      <c r="K61" s="4">
-        <v>9</v>
-      </c>
-      <c r="L61" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M61" s="11"/>
-      <c r="N61" s="11"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D62" s="3">
-        <v>17</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>17</v>
-      </c>
-      <c r="G62" s="3">
-        <v>16</v>
-      </c>
-      <c r="H62" s="3">
-        <v>16</v>
-      </c>
-      <c r="I62" s="3">
-        <v>-1</v>
-      </c>
-      <c r="J62" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K62" s="3">
-        <v>8</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M62" s="10"/>
-      <c r="N62" s="10"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="D63" s="4">
-        <v>17</v>
-      </c>
-      <c r="E63" s="4">
-        <v>0</v>
-      </c>
-      <c r="F63" s="4">
-        <v>17</v>
-      </c>
-      <c r="G63" s="4">
-        <v>16</v>
-      </c>
-      <c r="H63" s="4">
-        <v>16</v>
-      </c>
-      <c r="I63" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J63" s="4">
-        <v>-1</v>
-      </c>
-      <c r="K63" s="4">
-        <v>8</v>
-      </c>
-      <c r="L63" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M63" s="11"/>
-      <c r="N63" s="11"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D64" s="3">
-        <v>17</v>
-      </c>
-      <c r="E64" s="3">
-        <v>0</v>
-      </c>
-      <c r="F64" s="3">
-        <v>17</v>
-      </c>
-      <c r="G64" s="3">
-        <v>16</v>
-      </c>
-      <c r="H64" s="3">
-        <v>16</v>
-      </c>
-      <c r="I64" s="3">
-        <v>-1</v>
-      </c>
-      <c r="J64" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K64" s="3">
-        <v>8</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M64" s="10"/>
-      <c r="N64" s="10"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="D65" s="4">
-        <v>17</v>
-      </c>
-      <c r="E65" s="4">
-        <v>0</v>
-      </c>
-      <c r="F65" s="4">
-        <v>17</v>
-      </c>
-      <c r="G65" s="4">
-        <v>14</v>
-      </c>
-      <c r="H65" s="4">
-        <v>14</v>
-      </c>
-      <c r="I65" s="4">
-        <v>-3</v>
-      </c>
-      <c r="J65" s="4">
-        <v>-3</v>
-      </c>
-      <c r="K65" s="4">
-        <v>14</v>
-      </c>
-      <c r="L65" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M65" s="11"/>
-      <c r="N65" s="11"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="D66" s="3">
-        <v>17</v>
-      </c>
-      <c r="E66" s="3">
-        <v>0</v>
-      </c>
-      <c r="F66" s="3">
-        <v>17</v>
-      </c>
-      <c r="G66" s="3">
-        <v>14</v>
-      </c>
-      <c r="H66" s="3">
-        <v>14</v>
-      </c>
-      <c r="I66" s="3">
-        <v>-3</v>
-      </c>
-      <c r="J66" s="3">
-        <v>-3</v>
-      </c>
-      <c r="K66" s="3">
-        <v>14</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M66" s="10"/>
-      <c r="N66" s="10"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="D67" s="4">
-        <v>17</v>
-      </c>
-      <c r="E67" s="4">
-        <v>0</v>
-      </c>
-      <c r="F67" s="4">
-        <v>17</v>
-      </c>
-      <c r="G67" s="4">
-        <v>14</v>
-      </c>
-      <c r="H67" s="4">
-        <v>14</v>
-      </c>
-      <c r="I67" s="4">
-        <v>-3</v>
-      </c>
-      <c r="J67" s="4">
-        <v>-3</v>
-      </c>
-      <c r="K67" s="4">
-        <v>14</v>
-      </c>
-      <c r="L67" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M67" s="11"/>
-      <c r="N67" s="11"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D68" s="3">
-        <v>17</v>
-      </c>
-      <c r="E68" s="3">
-        <v>0</v>
-      </c>
-      <c r="F68" s="3">
-        <v>17</v>
-      </c>
-      <c r="G68" s="3">
-        <v>56</v>
-      </c>
-      <c r="H68" s="3">
-        <v>56</v>
-      </c>
-      <c r="I68" s="10">
-        <v>39</v>
-      </c>
-      <c r="J68" s="10">
-        <v>39</v>
-      </c>
-      <c r="K68" s="3">
-        <v>28</v>
-      </c>
-      <c r="L68" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M68" s="10"/>
-      <c r="N68" s="10"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="D69" s="4">
-        <v>17</v>
-      </c>
-      <c r="E69" s="4">
-        <v>0</v>
-      </c>
-      <c r="F69" s="4">
-        <v>17</v>
-      </c>
-      <c r="G69" s="4">
-        <v>28</v>
-      </c>
-      <c r="H69" s="4">
-        <v>28</v>
-      </c>
-      <c r="I69" s="11">
-        <v>11</v>
-      </c>
-      <c r="J69" s="11">
-        <v>11</v>
-      </c>
-      <c r="K69" s="4">
-        <v>28</v>
-      </c>
-      <c r="L69" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M69" s="11"/>
-      <c r="N69" s="11"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D70" s="3">
-        <v>17</v>
-      </c>
-      <c r="E70" s="3">
-        <v>0</v>
-      </c>
-      <c r="F70" s="3">
-        <v>17</v>
-      </c>
-      <c r="G70" s="3">
-        <v>56</v>
-      </c>
-      <c r="H70" s="3">
-        <v>56</v>
-      </c>
-      <c r="I70" s="10">
-        <v>39</v>
-      </c>
-      <c r="J70" s="10">
-        <v>39</v>
-      </c>
-      <c r="K70" s="3">
-        <v>28</v>
-      </c>
-      <c r="L70" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M70" s="10"/>
-      <c r="N70" s="10"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="D71" s="4">
-        <v>17</v>
-      </c>
-      <c r="E71" s="4">
-        <v>0</v>
-      </c>
-      <c r="F71" s="4">
-        <v>17</v>
-      </c>
-      <c r="G71" s="4">
-        <v>28</v>
-      </c>
-      <c r="H71" s="4">
-        <v>28</v>
-      </c>
-      <c r="I71" s="11">
-        <v>11</v>
-      </c>
-      <c r="J71" s="11">
-        <v>11</v>
-      </c>
-      <c r="K71" s="4">
-        <v>28</v>
-      </c>
-      <c r="L71" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M71" s="11"/>
-      <c r="N71" s="11"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D72" s="3">
-        <v>17</v>
-      </c>
-      <c r="E72" s="3">
-        <v>0</v>
-      </c>
-      <c r="F72" s="3">
-        <v>17</v>
-      </c>
-      <c r="G72" s="3">
-        <v>56</v>
-      </c>
-      <c r="H72" s="3">
-        <v>56</v>
-      </c>
-      <c r="I72" s="10">
-        <v>39</v>
-      </c>
-      <c r="J72" s="10">
-        <v>39</v>
-      </c>
-      <c r="K72" s="3">
-        <v>28</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M72" s="10"/>
-      <c r="N72" s="10"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="D73" s="4">
-        <v>17</v>
-      </c>
-      <c r="E73" s="4">
-        <v>0</v>
-      </c>
-      <c r="F73" s="4">
-        <v>17</v>
-      </c>
-      <c r="G73" s="4">
-        <v>28</v>
-      </c>
-      <c r="H73" s="4">
-        <v>28</v>
-      </c>
-      <c r="I73" s="11">
-        <v>11</v>
-      </c>
-      <c r="J73" s="11">
-        <v>11</v>
-      </c>
-      <c r="K73" s="4">
-        <v>28</v>
-      </c>
-      <c r="L73" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M73" s="11"/>
-      <c r="N73" s="11"/>
+      <c r="N76" t="s">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Du_lieu_mau_GDPT2018_30lop.xlsx
+++ b/Du_lieu_mau_GDPT2018_30lop.xlsx
@@ -7049,10 +7049,10 @@
         <v>43</v>
       </c>
       <c r="I3" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>103</v>
@@ -7193,7 +7193,7 @@
         <v>2</v>
       </c>
       <c r="J6" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>270</v>
@@ -7895,10 +7895,10 @@
         <v>43</v>
       </c>
       <c r="I21" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J21" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>109</v>
@@ -8039,7 +8039,7 @@
         <v>2</v>
       </c>
       <c r="J24" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>274</v>
@@ -8741,10 +8741,10 @@
         <v>43</v>
       </c>
       <c r="I39" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J39" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K39" s="3" t="s">
         <v>113</v>
@@ -8885,7 +8885,7 @@
         <v>2</v>
       </c>
       <c r="J42" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>277</v>
@@ -9587,10 +9587,10 @@
         <v>43</v>
       </c>
       <c r="I57" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J57" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>117</v>
@@ -9731,7 +9731,7 @@
         <v>2</v>
       </c>
       <c r="J60" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>281</v>
@@ -10433,10 +10433,10 @@
         <v>43</v>
       </c>
       <c r="I75" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J75" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K75" s="3" t="s">
         <v>121</v>
@@ -10577,7 +10577,7 @@
         <v>2</v>
       </c>
       <c r="J78" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K78" s="4" t="s">
         <v>284</v>
@@ -11232,10 +11232,10 @@
         <v>43</v>
       </c>
       <c r="I92" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J92" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K92" s="4" t="s">
         <v>125</v>
@@ -11376,7 +11376,7 @@
         <v>2</v>
       </c>
       <c r="J95" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K95" s="3" t="s">
         <v>270</v>
@@ -12031,10 +12031,10 @@
         <v>43</v>
       </c>
       <c r="I109" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J109" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K109" s="3" t="s">
         <v>129</v>
@@ -12175,7 +12175,7 @@
         <v>2</v>
       </c>
       <c r="J112" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K112" s="4" t="s">
         <v>274</v>
@@ -12830,10 +12830,10 @@
         <v>43</v>
       </c>
       <c r="I126" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J126" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K126" s="4" t="s">
         <v>133</v>
@@ -12974,7 +12974,7 @@
         <v>2</v>
       </c>
       <c r="J129" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K129" s="3" t="s">
         <v>277</v>
@@ -13535,10 +13535,10 @@
         <v>43</v>
       </c>
       <c r="I141" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J141" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K141" s="3" t="s">
         <v>137</v>
@@ -13679,7 +13679,7 @@
         <v>2</v>
       </c>
       <c r="J144" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K144" s="4" t="s">
         <v>281</v>
@@ -14240,10 +14240,10 @@
         <v>43</v>
       </c>
       <c r="I156" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J156" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K156" s="4" t="s">
         <v>141</v>
@@ -14384,7 +14384,7 @@
         <v>2</v>
       </c>
       <c r="J159" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K159" s="3" t="s">
         <v>284</v>
@@ -14945,10 +14945,10 @@
         <v>43</v>
       </c>
       <c r="I171" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J171" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K171" s="4" t="s">
         <v>121</v>
@@ -15089,7 +15089,7 @@
         <v>2</v>
       </c>
       <c r="J174" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K174" s="3" t="s">
         <v>284</v>
@@ -15791,10 +15791,10 @@
         <v>43</v>
       </c>
       <c r="I189" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J189" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K189" s="4" t="s">
         <v>125</v>
@@ -15935,7 +15935,7 @@
         <v>2</v>
       </c>
       <c r="J192" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K192" s="3" t="s">
         <v>270</v>
@@ -16637,10 +16637,10 @@
         <v>43</v>
       </c>
       <c r="I207" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J207" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K207" s="4" t="s">
         <v>129</v>
@@ -16781,7 +16781,7 @@
         <v>2</v>
       </c>
       <c r="J210" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K210" s="3" t="s">
         <v>274</v>
@@ -17483,10 +17483,10 @@
         <v>43</v>
       </c>
       <c r="I225" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J225" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K225" s="4" t="s">
         <v>133</v>
@@ -17627,7 +17627,7 @@
         <v>2</v>
       </c>
       <c r="J228" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K228" s="3" t="s">
         <v>277</v>
@@ -18329,10 +18329,10 @@
         <v>43</v>
       </c>
       <c r="I243" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J243" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K243" s="4" t="s">
         <v>137</v>
@@ -18473,7 +18473,7 @@
         <v>2</v>
       </c>
       <c r="J246" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K246" s="3" t="s">
         <v>281</v>
@@ -19128,10 +19128,10 @@
         <v>43</v>
       </c>
       <c r="I260" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J260" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K260" s="3" t="s">
         <v>141</v>
@@ -19272,7 +19272,7 @@
         <v>2</v>
       </c>
       <c r="J263" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K263" s="4" t="s">
         <v>284</v>
@@ -19927,10 +19927,10 @@
         <v>43</v>
       </c>
       <c r="I277" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J277" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K277" s="4" t="s">
         <v>103</v>
@@ -20071,7 +20071,7 @@
         <v>2</v>
       </c>
       <c r="J280" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K280" s="3" t="s">
         <v>270</v>
@@ -20726,10 +20726,10 @@
         <v>43</v>
       </c>
       <c r="I294" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J294" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K294" s="3" t="s">
         <v>109</v>
@@ -20870,7 +20870,7 @@
         <v>2</v>
       </c>
       <c r="J297" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K297" s="4" t="s">
         <v>274</v>
@@ -21431,10 +21431,10 @@
         <v>43</v>
       </c>
       <c r="I309" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J309" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K309" s="4" t="s">
         <v>113</v>
@@ -21575,7 +21575,7 @@
         <v>2</v>
       </c>
       <c r="J312" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K312" s="3" t="s">
         <v>277</v>
@@ -22136,10 +22136,10 @@
         <v>43</v>
       </c>
       <c r="I324" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J324" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K324" s="3" t="s">
         <v>137</v>
@@ -22280,7 +22280,7 @@
         <v>2</v>
       </c>
       <c r="J327" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K327" s="4" t="s">
         <v>281</v>
@@ -22982,10 +22982,10 @@
         <v>43</v>
       </c>
       <c r="I342" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J342" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K342" s="3" t="s">
         <v>141</v>
@@ -23126,7 +23126,7 @@
         <v>2</v>
       </c>
       <c r="J345" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K345" s="4" t="s">
         <v>284</v>
@@ -23828,10 +23828,10 @@
         <v>43</v>
       </c>
       <c r="I360" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J360" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K360" s="3" t="s">
         <v>103</v>
@@ -23972,7 +23972,7 @@
         <v>2</v>
       </c>
       <c r="J363" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K363" s="4" t="s">
         <v>270</v>
@@ -24674,10 +24674,10 @@
         <v>43</v>
       </c>
       <c r="I378" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J378" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K378" s="3" t="s">
         <v>109</v>
@@ -24818,7 +24818,7 @@
         <v>2</v>
       </c>
       <c r="J381" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K381" s="4" t="s">
         <v>274</v>
@@ -25520,10 +25520,10 @@
         <v>43</v>
       </c>
       <c r="I396" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J396" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K396" s="3" t="s">
         <v>113</v>
@@ -25664,7 +25664,7 @@
         <v>2</v>
       </c>
       <c r="J399" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K399" s="4" t="s">
         <v>277</v>
@@ -26319,10 +26319,10 @@
         <v>43</v>
       </c>
       <c r="I413" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J413" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K413" s="4" t="s">
         <v>117</v>
@@ -26463,7 +26463,7 @@
         <v>2</v>
       </c>
       <c r="J416" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K416" s="3" t="s">
         <v>281</v>
@@ -27118,10 +27118,10 @@
         <v>43</v>
       </c>
       <c r="I430" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J430" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K430" s="3" t="s">
         <v>121</v>
@@ -27262,7 +27262,7 @@
         <v>2</v>
       </c>
       <c r="J433" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K433" s="4" t="s">
         <v>284</v>
@@ -27917,10 +27917,10 @@
         <v>43</v>
       </c>
       <c r="I447" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J447" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K447" s="4" t="s">
         <v>125</v>
@@ -28061,7 +28061,7 @@
         <v>2</v>
       </c>
       <c r="J450" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K450" s="3" t="s">
         <v>270</v>
@@ -28622,10 +28622,10 @@
         <v>43</v>
       </c>
       <c r="I462" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J462" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K462" s="3" t="s">
         <v>129</v>
@@ -28766,7 +28766,7 @@
         <v>2</v>
       </c>
       <c r="J465" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K465" s="4" t="s">
         <v>274</v>
@@ -29327,10 +29327,10 @@
         <v>43</v>
       </c>
       <c r="I477" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J477" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K477" s="4" t="s">
         <v>133</v>
@@ -29471,7 +29471,7 @@
         <v>2</v>
       </c>
       <c r="J480" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K480" s="3" t="s">
         <v>277</v>
@@ -30032,10 +30032,10 @@
         <v>43</v>
       </c>
       <c r="I492" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J492" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K492" s="3" t="s">
         <v>137</v>
@@ -30176,7 +30176,7 @@
         <v>2</v>
       </c>
       <c r="J495" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K495" s="4" t="s">
         <v>281</v>
@@ -32153,19 +32153,19 @@
         <v>17</v>
       </c>
       <c r="G3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I3">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="J3">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="K3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L3">
         <v>3</v>
@@ -32197,19 +32197,19 @@
         <v>17</v>
       </c>
       <c r="G4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="J4">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="K4">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L4">
         <v>3</v>
@@ -32241,19 +32241,19 @@
         <v>17</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H5">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="J5">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="K5">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L5">
         <v>3</v>
@@ -32285,19 +32285,19 @@
         <v>17</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="J6">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="K6">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -32329,19 +32329,19 @@
         <v>17</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="J7">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="K7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L7">
         <v>3</v>
@@ -32373,19 +32373,19 @@
         <v>17</v>
       </c>
       <c r="G8">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H8">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="J8">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="K8">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L8">
         <v>3</v>
@@ -32417,19 +32417,19 @@
         <v>17</v>
       </c>
       <c r="G9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="J9">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="K9">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L9">
         <v>3</v>
@@ -32461,19 +32461,19 @@
         <v>17</v>
       </c>
       <c r="G10">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H10">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="J10">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="K10">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L10">
         <v>3</v>
@@ -32505,19 +32505,19 @@
         <v>17</v>
       </c>
       <c r="G11">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H11">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="K11">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="L11">
         <v>4</v>
@@ -32549,19 +32549,19 @@
         <v>14</v>
       </c>
       <c r="G12">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H12">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I12">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="J12">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="K12">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L12">
         <v>3</v>
@@ -33872,16 +33872,16 @@
         <v>12</v>
       </c>
       <c r="H42">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I42">
         <v>-5</v>
       </c>
       <c r="J42">
-        <v>-5</v>
+        <v>-11</v>
       </c>
       <c r="K42">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L42">
         <v>6</v>
@@ -33916,16 +33916,16 @@
         <v>12</v>
       </c>
       <c r="H43">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I43">
         <v>-5</v>
       </c>
       <c r="J43">
-        <v>-5</v>
+        <v>-11</v>
       </c>
       <c r="K43">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L43">
         <v>6</v>
@@ -33960,16 +33960,16 @@
         <v>12</v>
       </c>
       <c r="H44">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I44">
         <v>-5</v>
       </c>
       <c r="J44">
-        <v>-5</v>
+        <v>-11</v>
       </c>
       <c r="K44">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L44">
         <v>6</v>
@@ -34004,16 +34004,16 @@
         <v>12</v>
       </c>
       <c r="H45">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I45">
         <v>-5</v>
       </c>
       <c r="J45">
-        <v>-5</v>
+        <v>-11</v>
       </c>
       <c r="K45">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L45">
         <v>6</v>
@@ -34048,16 +34048,16 @@
         <v>12</v>
       </c>
       <c r="H46">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I46">
         <v>-5</v>
       </c>
       <c r="J46">
-        <v>-5</v>
+        <v>-11</v>
       </c>
       <c r="K46">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L46">
         <v>6</v>

--- a/Du_lieu_mau_GDPT2018_30lop.xlsx
+++ b/Du_lieu_mau_GDPT2018_30lop.xlsx
@@ -7102,16 +7102,16 @@
         <v>3</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="O4" s="4" t="s">
         <v>60</v>
@@ -7196,16 +7196,16 @@
         <v>1</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="O6" s="4" t="s">
         <v>60</v>
@@ -7384,16 +7384,16 @@
         <v>1</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="O10" s="4" t="s">
         <v>60</v>
@@ -7525,16 +7525,16 @@
         <v>1</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="O13" s="3" t="s">
         <v>477</v>
@@ -7572,16 +7572,16 @@
         <v>2</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="O14" s="4" t="s">
         <v>480</v>
@@ -7666,16 +7666,16 @@
         <v>2</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="O16" s="4" t="s">
         <v>480</v>
@@ -7807,16 +7807,16 @@
         <v>1</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="O19" s="3" t="s">
         <v>477</v>
@@ -7854,16 +7854,16 @@
         <v>1</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="O20" s="4" t="s">
         <v>480</v>
@@ -7948,16 +7948,16 @@
         <v>3</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="O22" s="4" t="s">
         <v>60</v>
@@ -8042,16 +8042,16 @@
         <v>1</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="O24" s="4" t="s">
         <v>60</v>
@@ -8230,16 +8230,16 @@
         <v>1</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="O28" s="4" t="s">
         <v>60</v>
@@ -8371,16 +8371,16 @@
         <v>1</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="O31" s="3" t="s">
         <v>477</v>
@@ -8418,16 +8418,16 @@
         <v>2</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="O32" s="4" t="s">
         <v>480</v>
@@ -8465,16 +8465,16 @@
         <v>1</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>477</v>
@@ -8512,16 +8512,16 @@
         <v>2</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="O34" s="4" t="s">
         <v>480</v>
@@ -8653,16 +8653,16 @@
         <v>1</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="O37" s="3" t="s">
         <v>477</v>
@@ -8700,16 +8700,16 @@
         <v>1</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="O38" s="4" t="s">
         <v>480</v>
@@ -8794,16 +8794,16 @@
         <v>3</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="O40" s="4" t="s">
         <v>60</v>
@@ -8841,16 +8841,16 @@
         <v>3</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>60</v>
@@ -8888,16 +8888,16 @@
         <v>1</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="O42" s="4" t="s">
         <v>60</v>
@@ -8982,16 +8982,16 @@
         <v>1</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="O44" s="4" t="s">
         <v>474</v>
@@ -9076,16 +9076,16 @@
         <v>1</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="O46" s="4" t="s">
         <v>60</v>
@@ -9217,16 +9217,16 @@
         <v>1</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>477</v>
@@ -9264,16 +9264,16 @@
         <v>2</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="O50" s="4" t="s">
         <v>480</v>
@@ -9358,16 +9358,16 @@
         <v>2</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="O52" s="4" t="s">
         <v>480</v>
@@ -9405,16 +9405,16 @@
         <v>1</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="O53" s="3" t="s">
         <v>477</v>
@@ -9452,16 +9452,16 @@
         <v>2</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="O54" s="4" t="s">
         <v>480</v>
@@ -9499,16 +9499,16 @@
         <v>1</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>385</v>
+        <v>314</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>386</v>
+        <v>315</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>385</v>
+        <v>314</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>386</v>
+        <v>315</v>
       </c>
       <c r="O55" s="3" t="s">
         <v>477</v>
@@ -9546,16 +9546,16 @@
         <v>1</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="M56" s="4" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="N56" s="4" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="O56" s="4" t="s">
         <v>480</v>
@@ -9640,16 +9640,16 @@
         <v>3</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="M58" s="4" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="N58" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="O58" s="4" t="s">
         <v>60</v>
@@ -9687,16 +9687,16 @@
         <v>3</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>60</v>
@@ -9828,16 +9828,16 @@
         <v>1</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="N62" s="4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="O62" s="4" t="s">
         <v>474</v>
@@ -10063,16 +10063,16 @@
         <v>1</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="O67" s="3" t="s">
         <v>477</v>
@@ -10110,16 +10110,16 @@
         <v>2</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="M68" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="N68" s="4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="O68" s="4" t="s">
         <v>480</v>
@@ -10204,16 +10204,16 @@
         <v>2</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="M70" s="4" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="N70" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="O70" s="4" t="s">
         <v>480</v>
@@ -10251,16 +10251,16 @@
         <v>1</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="O71" s="3" t="s">
         <v>477</v>
@@ -10298,16 +10298,16 @@
         <v>2</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="M72" s="4" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="N72" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="O72" s="4" t="s">
         <v>480</v>
@@ -10345,16 +10345,16 @@
         <v>1</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="O73" s="3" t="s">
         <v>477</v>
@@ -10392,16 +10392,16 @@
         <v>1</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M74" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="N74" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="O74" s="4" t="s">
         <v>480</v>
@@ -10486,16 +10486,16 @@
         <v>3</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="M76" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="N76" s="4" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="O76" s="4" t="s">
         <v>60</v>
@@ -10533,16 +10533,16 @@
         <v>3</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="N77" s="3" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="O77" s="3" t="s">
         <v>60</v>
@@ -10580,16 +10580,16 @@
         <v>1</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="M78" s="4" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="N78" s="4" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="O78" s="4" t="s">
         <v>60</v>
@@ -10627,16 +10627,16 @@
         <v>2</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="O79" s="3" t="s">
         <v>474</v>
@@ -10674,16 +10674,16 @@
         <v>1</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="M80" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="N80" s="4" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="O80" s="4" t="s">
         <v>474</v>
@@ -10768,16 +10768,16 @@
         <v>1</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="M82" s="4" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="N82" s="4" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="O82" s="4" t="s">
         <v>60</v>
@@ -10909,16 +10909,16 @@
         <v>1</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="O85" s="3" t="s">
         <v>477</v>
@@ -10956,16 +10956,16 @@
         <v>2</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="M86" s="4" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="N86" s="4" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="O86" s="4" t="s">
         <v>480</v>
@@ -11003,16 +11003,16 @@
         <v>1</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="N87" s="3" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="O87" s="3" t="s">
         <v>477</v>
@@ -11050,16 +11050,16 @@
         <v>2</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="M88" s="4" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="N88" s="4" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="O88" s="4" t="s">
         <v>480</v>
@@ -11097,16 +11097,16 @@
         <v>1</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>477</v>
@@ -11285,16 +11285,16 @@
         <v>3</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="N93" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="O93" s="3" t="s">
         <v>60</v>
@@ -11332,16 +11332,16 @@
         <v>3</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="M94" s="4" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="N94" s="4" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="O94" s="4" t="s">
         <v>60</v>
@@ -11426,16 +11426,16 @@
         <v>2</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="M96" s="4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="N96" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="O96" s="4" t="s">
         <v>474</v>
@@ -11473,16 +11473,16 @@
         <v>1</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="O97" s="3" t="s">
         <v>474</v>
@@ -11567,16 +11567,16 @@
         <v>1</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="N99" s="3" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="O99" s="3" t="s">
         <v>60</v>
@@ -11849,16 +11849,16 @@
         <v>2</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="M105" s="3" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="N105" s="3" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="O105" s="3" t="s">
         <v>480</v>
@@ -11896,16 +11896,16 @@
         <v>1</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>385</v>
+        <v>317</v>
       </c>
       <c r="L106" s="4" t="s">
-        <v>386</v>
+        <v>318</v>
       </c>
       <c r="M106" s="4" t="s">
-        <v>385</v>
+        <v>317</v>
       </c>
       <c r="N106" s="4" t="s">
-        <v>386</v>
+        <v>318</v>
       </c>
       <c r="O106" s="4" t="s">
         <v>477</v>
@@ -12084,16 +12084,16 @@
         <v>3</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="L110" s="4" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="M110" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="N110" s="4" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="O110" s="4" t="s">
         <v>60</v>
@@ -12131,16 +12131,16 @@
         <v>3</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="N111" s="3" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="O111" s="3" t="s">
         <v>60</v>
@@ -12225,16 +12225,16 @@
         <v>2</v>
       </c>
       <c r="K113" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="M113" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="N113" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="O113" s="3" t="s">
         <v>474</v>
@@ -12319,16 +12319,16 @@
         <v>3</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="L115" s="3" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="M115" s="3" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="N115" s="3" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="O115" s="3" t="s">
         <v>60</v>
@@ -12366,16 +12366,16 @@
         <v>1</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="M116" s="4" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="N116" s="4" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="O116" s="4" t="s">
         <v>60</v>
@@ -12507,16 +12507,16 @@
         <v>1</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="L119" s="3" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="M119" s="3" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="N119" s="3" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="O119" s="3" t="s">
         <v>477</v>
@@ -12601,16 +12601,16 @@
         <v>1</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="M121" s="3" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="N121" s="3" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="O121" s="3" t="s">
         <v>477</v>
@@ -12648,16 +12648,16 @@
         <v>2</v>
       </c>
       <c r="K122" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="L122" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="M122" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="N122" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="O122" s="4" t="s">
         <v>480</v>
@@ -12695,16 +12695,16 @@
         <v>1</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="L123" s="3" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="M123" s="3" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="N123" s="3" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="O123" s="3" t="s">
         <v>477</v>
@@ -12742,16 +12742,16 @@
         <v>2</v>
       </c>
       <c r="K124" s="4" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="L124" s="4" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="M124" s="4" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="N124" s="4" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="O124" s="4" t="s">
         <v>480</v>
@@ -12883,16 +12883,16 @@
         <v>3</v>
       </c>
       <c r="K127" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="L127" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="M127" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="N127" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="O127" s="3" t="s">
         <v>60</v>
@@ -12930,16 +12930,16 @@
         <v>3</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="L128" s="4" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="M128" s="4" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="N128" s="4" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="O128" s="4" t="s">
         <v>60</v>
@@ -12977,16 +12977,16 @@
         <v>1</v>
       </c>
       <c r="K129" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="L129" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="M129" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="N129" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="O129" s="3" t="s">
         <v>60</v>
@@ -13024,16 +13024,16 @@
         <v>2</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="M130" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="N130" s="4" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="O130" s="4" t="s">
         <v>474</v>
@@ -13118,16 +13118,16 @@
         <v>3</v>
       </c>
       <c r="K132" s="4" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="L132" s="4" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="M132" s="4" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="N132" s="4" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="O132" s="4" t="s">
         <v>60</v>
@@ -13165,16 +13165,16 @@
         <v>1</v>
       </c>
       <c r="K133" s="3" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="L133" s="3" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="M133" s="3" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="N133" s="3" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="O133" s="3" t="s">
         <v>60</v>
@@ -13588,16 +13588,16 @@
         <v>3</v>
       </c>
       <c r="K142" s="4" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="L142" s="4" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="M142" s="4" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="N142" s="4" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="O142" s="4" t="s">
         <v>60</v>
@@ -13635,16 +13635,16 @@
         <v>3</v>
       </c>
       <c r="K143" s="3" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="L143" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="M143" s="3" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="N143" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="O143" s="3" t="s">
         <v>60</v>
@@ -13682,16 +13682,16 @@
         <v>1</v>
       </c>
       <c r="K144" s="4" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="L144" s="4" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="M144" s="4" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="N144" s="4" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="O144" s="4" t="s">
         <v>60</v>
@@ -13729,16 +13729,16 @@
         <v>2</v>
       </c>
       <c r="K145" s="3" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="L145" s="3" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="M145" s="3" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="N145" s="3" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="O145" s="3" t="s">
         <v>474</v>
@@ -13776,16 +13776,16 @@
         <v>1</v>
       </c>
       <c r="K146" s="4" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="L146" s="4" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="M146" s="4" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="N146" s="4" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="O146" s="4" t="s">
         <v>474</v>
@@ -13823,16 +13823,16 @@
         <v>3</v>
       </c>
       <c r="K147" s="3" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="L147" s="3" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="M147" s="3" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="N147" s="3" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="O147" s="3" t="s">
         <v>60</v>
@@ -13870,16 +13870,16 @@
         <v>1</v>
       </c>
       <c r="K148" s="4" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="L148" s="4" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="M148" s="4" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="N148" s="4" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="O148" s="4" t="s">
         <v>60</v>
@@ -14058,16 +14058,16 @@
         <v>3</v>
       </c>
       <c r="K152" s="4" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="L152" s="4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M152" s="4" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="N152" s="4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="O152" s="4" t="s">
         <v>60</v>
@@ -14105,16 +14105,16 @@
         <v>2</v>
       </c>
       <c r="K153" s="3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="L153" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="M153" s="3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="N153" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="O153" s="3" t="s">
         <v>60</v>
@@ -14293,16 +14293,16 @@
         <v>3</v>
       </c>
       <c r="K157" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="L157" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="M157" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="N157" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="O157" s="3" t="s">
         <v>60</v>
@@ -14340,16 +14340,16 @@
         <v>3</v>
       </c>
       <c r="K158" s="4" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="L158" s="4" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="M158" s="4" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="N158" s="4" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="O158" s="4" t="s">
         <v>60</v>
@@ -14387,16 +14387,16 @@
         <v>1</v>
       </c>
       <c r="K159" s="3" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="L159" s="3" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="M159" s="3" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="N159" s="3" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="O159" s="3" t="s">
         <v>60</v>
@@ -14434,16 +14434,16 @@
         <v>2</v>
       </c>
       <c r="K160" s="4" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="L160" s="4" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="M160" s="4" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="N160" s="4" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="O160" s="4" t="s">
         <v>474</v>
@@ -14481,16 +14481,16 @@
         <v>1</v>
       </c>
       <c r="K161" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="L161" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="M161" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="N161" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="O161" s="3" t="s">
         <v>474</v>
@@ -14528,16 +14528,16 @@
         <v>3</v>
       </c>
       <c r="K162" s="4" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="L162" s="4" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="M162" s="4" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="N162" s="4" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="O162" s="4" t="s">
         <v>60</v>
@@ -14575,16 +14575,16 @@
         <v>1</v>
       </c>
       <c r="K163" s="3" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="L163" s="3" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="M163" s="3" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="N163" s="3" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="O163" s="3" t="s">
         <v>60</v>
@@ -14904,16 +14904,16 @@
         <v>2</v>
       </c>
       <c r="K170" s="4" t="s">
-        <v>385</v>
+        <v>307</v>
       </c>
       <c r="L170" s="4" t="s">
-        <v>386</v>
+        <v>308</v>
       </c>
       <c r="M170" s="4" t="s">
-        <v>385</v>
+        <v>307</v>
       </c>
       <c r="N170" s="4" t="s">
-        <v>386</v>
+        <v>308</v>
       </c>
       <c r="O170" s="4" t="s">
         <v>480</v>
@@ -14951,16 +14951,16 @@
         <v>3</v>
       </c>
       <c r="K171" s="4" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="L171" s="4" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="M171" s="4" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="N171" s="4" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="O171" s="4" t="s">
         <v>60</v>
@@ -14998,16 +14998,16 @@
         <v>3</v>
       </c>
       <c r="K172" s="3" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="L172" s="3" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="M172" s="3" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="N172" s="3" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="O172" s="3" t="s">
         <v>60</v>
@@ -15045,16 +15045,16 @@
         <v>3</v>
       </c>
       <c r="K173" s="4" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="L173" s="4" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="M173" s="4" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="N173" s="4" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="O173" s="4" t="s">
         <v>60</v>
@@ -15233,16 +15233,16 @@
         <v>3</v>
       </c>
       <c r="K177" s="4" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="L177" s="4" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="M177" s="4" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="N177" s="4" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="O177" s="4" t="s">
         <v>60</v>
@@ -15421,16 +15421,16 @@
         <v>1</v>
       </c>
       <c r="K181" s="4" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L181" s="4" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="M181" s="4" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="N181" s="4" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="O181" s="4" t="s">
         <v>477</v>
@@ -15468,16 +15468,16 @@
         <v>2</v>
       </c>
       <c r="K182" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="L182" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="M182" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="N182" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="O182" s="3" t="s">
         <v>480</v>
@@ -15562,16 +15562,16 @@
         <v>2</v>
       </c>
       <c r="K184" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L184" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="M184" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="N184" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="O184" s="3" t="s">
         <v>480</v>
@@ -15609,16 +15609,16 @@
         <v>1</v>
       </c>
       <c r="K185" s="4" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="L185" s="4" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="M185" s="4" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="N185" s="4" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="O185" s="4" t="s">
         <v>477</v>
@@ -15656,16 +15656,16 @@
         <v>2</v>
       </c>
       <c r="K186" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="L186" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="M186" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="N186" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="O186" s="3" t="s">
         <v>480</v>
@@ -15703,16 +15703,16 @@
         <v>1</v>
       </c>
       <c r="K187" s="4" t="s">
-        <v>317</v>
+        <v>385</v>
       </c>
       <c r="L187" s="4" t="s">
-        <v>318</v>
+        <v>386</v>
       </c>
       <c r="M187" s="4" t="s">
-        <v>317</v>
+        <v>385</v>
       </c>
       <c r="N187" s="4" t="s">
-        <v>318</v>
+        <v>386</v>
       </c>
       <c r="O187" s="4" t="s">
         <v>477</v>
@@ -15797,16 +15797,16 @@
         <v>3</v>
       </c>
       <c r="K189" s="4" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="L189" s="4" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="M189" s="4" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="N189" s="4" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="O189" s="4" t="s">
         <v>60</v>
@@ -15844,16 +15844,16 @@
         <v>3</v>
       </c>
       <c r="K190" s="3" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="L190" s="3" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="M190" s="3" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="N190" s="3" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="O190" s="3" t="s">
         <v>60</v>
@@ -15891,16 +15891,16 @@
         <v>3</v>
       </c>
       <c r="K191" s="4" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="L191" s="4" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="M191" s="4" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="N191" s="4" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="O191" s="4" t="s">
         <v>60</v>
@@ -15938,16 +15938,16 @@
         <v>1</v>
       </c>
       <c r="K192" s="3" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="L192" s="3" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="M192" s="3" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="N192" s="3" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="O192" s="3" t="s">
         <v>60</v>
@@ -15985,16 +15985,16 @@
         <v>2</v>
       </c>
       <c r="K193" s="4" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="L193" s="4" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="M193" s="4" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="N193" s="4" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="O193" s="4" t="s">
         <v>474</v>
@@ -16032,16 +16032,16 @@
         <v>1</v>
       </c>
       <c r="K194" s="3" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="L194" s="3" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="M194" s="3" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="N194" s="3" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="O194" s="3" t="s">
         <v>474</v>
@@ -16079,16 +16079,16 @@
         <v>3</v>
       </c>
       <c r="K195" s="4" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="L195" s="4" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="M195" s="4" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="N195" s="4" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="O195" s="4" t="s">
         <v>60</v>
@@ -16267,16 +16267,16 @@
         <v>1</v>
       </c>
       <c r="K199" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="L199" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="M199" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="N199" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="O199" s="4" t="s">
         <v>477</v>
@@ -16361,16 +16361,16 @@
         <v>1</v>
       </c>
       <c r="K201" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="L201" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="M201" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="N201" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="O201" s="4" t="s">
         <v>477</v>
@@ -16408,16 +16408,16 @@
         <v>2</v>
       </c>
       <c r="K202" s="3" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="L202" s="3" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="M202" s="3" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="N202" s="3" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="O202" s="3" t="s">
         <v>480</v>
@@ -16549,16 +16549,16 @@
         <v>1</v>
       </c>
       <c r="K205" s="4" t="s">
-        <v>307</v>
+        <v>385</v>
       </c>
       <c r="L205" s="4" t="s">
-        <v>308</v>
+        <v>386</v>
       </c>
       <c r="M205" s="4" t="s">
-        <v>307</v>
+        <v>385</v>
       </c>
       <c r="N205" s="4" t="s">
-        <v>308</v>
+        <v>386</v>
       </c>
       <c r="O205" s="4" t="s">
         <v>477</v>
@@ -16596,16 +16596,16 @@
         <v>1</v>
       </c>
       <c r="K206" s="3" t="s">
-        <v>311</v>
+        <v>385</v>
       </c>
       <c r="L206" s="3" t="s">
-        <v>312</v>
+        <v>386</v>
       </c>
       <c r="M206" s="3" t="s">
-        <v>311</v>
+        <v>385</v>
       </c>
       <c r="N206" s="3" t="s">
-        <v>312</v>
+        <v>386</v>
       </c>
       <c r="O206" s="3" t="s">
         <v>480</v>
@@ -16643,16 +16643,16 @@
         <v>3</v>
       </c>
       <c r="K207" s="4" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="L207" s="4" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="M207" s="4" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="N207" s="4" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="O207" s="4" t="s">
         <v>60</v>
@@ -16690,16 +16690,16 @@
         <v>3</v>
       </c>
       <c r="K208" s="3" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="L208" s="3" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="M208" s="3" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="N208" s="3" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="O208" s="3" t="s">
         <v>60</v>
@@ -16737,16 +16737,16 @@
         <v>3</v>
       </c>
       <c r="K209" s="4" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="L209" s="4" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="M209" s="4" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="N209" s="4" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="O209" s="4" t="s">
         <v>60</v>
@@ -16784,16 +16784,16 @@
         <v>1</v>
       </c>
       <c r="K210" s="3" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="L210" s="3" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="M210" s="3" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="N210" s="3" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="O210" s="3" t="s">
         <v>60</v>
@@ -16831,16 +16831,16 @@
         <v>2</v>
       </c>
       <c r="K211" s="4" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="L211" s="4" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="M211" s="4" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="N211" s="4" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="O211" s="4" t="s">
         <v>474</v>
@@ -16878,16 +16878,16 @@
         <v>1</v>
       </c>
       <c r="K212" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L212" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="M212" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="N212" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="O212" s="3" t="s">
         <v>474</v>
@@ -16925,16 +16925,16 @@
         <v>3</v>
       </c>
       <c r="K213" s="4" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="L213" s="4" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="M213" s="4" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="N213" s="4" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="O213" s="4" t="s">
         <v>60</v>
@@ -16972,16 +16972,16 @@
         <v>1</v>
       </c>
       <c r="K214" s="3" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="L214" s="3" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="M214" s="3" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="N214" s="3" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="O214" s="3" t="s">
         <v>60</v>
@@ -17160,16 +17160,16 @@
         <v>2</v>
       </c>
       <c r="K218" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="L218" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="M218" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="N218" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="O218" s="3" t="s">
         <v>480</v>
@@ -17254,16 +17254,16 @@
         <v>2</v>
       </c>
       <c r="K220" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="L220" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="M220" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="N220" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="O220" s="3" t="s">
         <v>480</v>
@@ -17301,16 +17301,16 @@
         <v>1</v>
       </c>
       <c r="K221" s="4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="L221" s="4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M221" s="4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="N221" s="4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="O221" s="4" t="s">
         <v>477</v>
@@ -17348,16 +17348,16 @@
         <v>2</v>
       </c>
       <c r="K222" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="L222" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M222" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="N222" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="O222" s="3" t="s">
         <v>480</v>
@@ -17395,16 +17395,16 @@
         <v>1</v>
       </c>
       <c r="K223" s="4" t="s">
-        <v>314</v>
+        <v>385</v>
       </c>
       <c r="L223" s="4" t="s">
-        <v>315</v>
+        <v>386</v>
       </c>
       <c r="M223" s="4" t="s">
-        <v>314</v>
+        <v>385</v>
       </c>
       <c r="N223" s="4" t="s">
-        <v>315</v>
+        <v>386</v>
       </c>
       <c r="O223" s="4" t="s">
         <v>477</v>
@@ -17442,16 +17442,16 @@
         <v>1</v>
       </c>
       <c r="K224" s="3" t="s">
-        <v>317</v>
+        <v>385</v>
       </c>
       <c r="L224" s="3" t="s">
-        <v>318</v>
+        <v>386</v>
       </c>
       <c r="M224" s="3" t="s">
-        <v>317</v>
+        <v>385</v>
       </c>
       <c r="N224" s="3" t="s">
-        <v>318</v>
+        <v>386</v>
       </c>
       <c r="O224" s="3" t="s">
         <v>480</v>
@@ -17489,16 +17489,16 @@
         <v>3</v>
       </c>
       <c r="K225" s="4" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="L225" s="4" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="M225" s="4" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="N225" s="4" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="O225" s="4" t="s">
         <v>60</v>
@@ -17536,16 +17536,16 @@
         <v>3</v>
       </c>
       <c r="K226" s="3" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="L226" s="3" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="M226" s="3" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="N226" s="3" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="O226" s="3" t="s">
         <v>60</v>
@@ -17583,16 +17583,16 @@
         <v>3</v>
       </c>
       <c r="K227" s="4" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="L227" s="4" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="M227" s="4" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="N227" s="4" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="O227" s="4" t="s">
         <v>60</v>
@@ -17630,16 +17630,16 @@
         <v>1</v>
       </c>
       <c r="K228" s="3" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="L228" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="M228" s="3" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="N228" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="O228" s="3" t="s">
         <v>60</v>
@@ -17677,16 +17677,16 @@
         <v>2</v>
       </c>
       <c r="K229" s="4" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="L229" s="4" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="M229" s="4" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="N229" s="4" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="O229" s="4" t="s">
         <v>474</v>
@@ -17771,16 +17771,16 @@
         <v>3</v>
       </c>
       <c r="K231" s="4" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="L231" s="4" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="M231" s="4" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="N231" s="4" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="O231" s="4" t="s">
         <v>60</v>
@@ -17818,16 +17818,16 @@
         <v>1</v>
       </c>
       <c r="K232" s="3" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="L232" s="3" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="M232" s="3" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="N232" s="3" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="O232" s="3" t="s">
         <v>60</v>
@@ -17959,16 +17959,16 @@
         <v>1</v>
       </c>
       <c r="K235" s="4" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="L235" s="4" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="M235" s="4" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="N235" s="4" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="O235" s="4" t="s">
         <v>477</v>
@@ -18006,16 +18006,16 @@
         <v>2</v>
       </c>
       <c r="K236" s="3" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="L236" s="3" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="M236" s="3" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="N236" s="3" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="O236" s="3" t="s">
         <v>480</v>
@@ -18053,16 +18053,16 @@
         <v>1</v>
       </c>
       <c r="K237" s="4" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="L237" s="4" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="M237" s="4" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="N237" s="4" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="O237" s="4" t="s">
         <v>477</v>
@@ -18100,16 +18100,16 @@
         <v>2</v>
       </c>
       <c r="K238" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="L238" s="3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="M238" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="N238" s="3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="O238" s="3" t="s">
         <v>480</v>
@@ -18147,16 +18147,16 @@
         <v>1</v>
       </c>
       <c r="K239" s="4" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="L239" s="4" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="M239" s="4" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="N239" s="4" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="O239" s="4" t="s">
         <v>477</v>
@@ -18194,16 +18194,16 @@
         <v>2</v>
       </c>
       <c r="K240" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="L240" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="M240" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="N240" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="O240" s="3" t="s">
         <v>480</v>
@@ -18288,16 +18288,16 @@
         <v>1</v>
       </c>
       <c r="K242" s="3" t="s">
-        <v>307</v>
+        <v>385</v>
       </c>
       <c r="L242" s="3" t="s">
-        <v>308</v>
+        <v>386</v>
       </c>
       <c r="M242" s="3" t="s">
-        <v>307</v>
+        <v>385</v>
       </c>
       <c r="N242" s="3" t="s">
-        <v>308</v>
+        <v>386</v>
       </c>
       <c r="O242" s="3" t="s">
         <v>480</v>
@@ -18335,16 +18335,16 @@
         <v>3</v>
       </c>
       <c r="K243" s="4" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="L243" s="4" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="M243" s="4" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="N243" s="4" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O243" s="4" t="s">
         <v>60</v>
@@ -18382,16 +18382,16 @@
         <v>3</v>
       </c>
       <c r="K244" s="3" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="L244" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="M244" s="3" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="N244" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="O244" s="3" t="s">
         <v>60</v>
@@ -18429,16 +18429,16 @@
         <v>3</v>
       </c>
       <c r="K245" s="4" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="L245" s="4" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="M245" s="4" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="N245" s="4" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="O245" s="4" t="s">
         <v>60</v>
@@ -18476,16 +18476,16 @@
         <v>1</v>
       </c>
       <c r="K246" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L246" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="M246" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N246" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="O246" s="3" t="s">
         <v>60</v>
@@ -18523,16 +18523,16 @@
         <v>2</v>
       </c>
       <c r="K247" s="4" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L247" s="4" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="M247" s="4" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="N247" s="4" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="O247" s="4" t="s">
         <v>474</v>
@@ -18570,16 +18570,16 @@
         <v>1</v>
       </c>
       <c r="K248" s="3" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="L248" s="3" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="M248" s="3" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="N248" s="3" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="O248" s="3" t="s">
         <v>474</v>
@@ -18664,16 +18664,16 @@
         <v>1</v>
       </c>
       <c r="K250" s="3" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="L250" s="3" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="M250" s="3" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="N250" s="3" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="O250" s="3" t="s">
         <v>60</v>
@@ -18805,16 +18805,16 @@
         <v>1</v>
       </c>
       <c r="K253" s="4" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="L253" s="4" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M253" s="4" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="N253" s="4" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="O253" s="4" t="s">
         <v>477</v>
@@ -18852,16 +18852,16 @@
         <v>2</v>
       </c>
       <c r="K254" s="3" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L254" s="3" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="M254" s="3" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="N254" s="3" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="O254" s="3" t="s">
         <v>480</v>
@@ -18899,16 +18899,16 @@
         <v>1</v>
       </c>
       <c r="K255" s="4" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="L255" s="4" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="M255" s="4" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="N255" s="4" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="O255" s="4" t="s">
         <v>477</v>
@@ -18946,16 +18946,16 @@
         <v>2</v>
       </c>
       <c r="K256" s="3" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="L256" s="3" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="M256" s="3" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="N256" s="3" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="O256" s="3" t="s">
         <v>480</v>
@@ -18993,16 +18993,16 @@
         <v>1</v>
       </c>
       <c r="K257" s="4" t="s">
-        <v>311</v>
+        <v>385</v>
       </c>
       <c r="L257" s="4" t="s">
-        <v>312</v>
+        <v>386</v>
       </c>
       <c r="M257" s="4" t="s">
-        <v>311</v>
+        <v>385</v>
       </c>
       <c r="N257" s="4" t="s">
-        <v>312</v>
+        <v>386</v>
       </c>
       <c r="O257" s="4" t="s">
         <v>477</v>
@@ -19040,16 +19040,16 @@
         <v>2</v>
       </c>
       <c r="K258" s="3" t="s">
-        <v>307</v>
+        <v>385</v>
       </c>
       <c r="L258" s="3" t="s">
-        <v>308</v>
+        <v>386</v>
       </c>
       <c r="M258" s="3" t="s">
-        <v>307</v>
+        <v>385</v>
       </c>
       <c r="N258" s="3" t="s">
-        <v>308</v>
+        <v>386</v>
       </c>
       <c r="O258" s="3" t="s">
         <v>480</v>
@@ -19087,16 +19087,16 @@
         <v>2</v>
       </c>
       <c r="K259" s="4" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="L259" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="M259" s="4" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="N259" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O259" s="4" t="s">
         <v>60</v>
@@ -19134,16 +19134,16 @@
         <v>3</v>
       </c>
       <c r="K260" s="3" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="L260" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="M260" s="3" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="N260" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="O260" s="3" t="s">
         <v>60</v>
@@ -19181,16 +19181,16 @@
         <v>3</v>
       </c>
       <c r="K261" s="4" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="L261" s="4" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="M261" s="4" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="N261" s="4" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="O261" s="4" t="s">
         <v>60</v>
@@ -19228,16 +19228,16 @@
         <v>3</v>
       </c>
       <c r="K262" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="L262" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="M262" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="N262" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O262" s="3" t="s">
         <v>60</v>
@@ -19369,16 +19369,16 @@
         <v>1</v>
       </c>
       <c r="K265" s="4" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L265" s="4" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="M265" s="4" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="N265" s="4" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="O265" s="4" t="s">
         <v>474</v>
@@ -19463,16 +19463,16 @@
         <v>1</v>
       </c>
       <c r="K267" s="4" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="L267" s="4" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="M267" s="4" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="N267" s="4" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="O267" s="4" t="s">
         <v>60</v>
@@ -19604,16 +19604,16 @@
         <v>1</v>
       </c>
       <c r="K270" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="L270" s="3" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="M270" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="N270" s="3" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="O270" s="3" t="s">
         <v>477</v>
@@ -19651,16 +19651,16 @@
         <v>2</v>
       </c>
       <c r="K271" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="L271" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="M271" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="N271" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="O271" s="4" t="s">
         <v>480</v>
@@ -19745,16 +19745,16 @@
         <v>2</v>
       </c>
       <c r="K273" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="L273" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="M273" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="N273" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="O273" s="4" t="s">
         <v>480</v>
@@ -19792,16 +19792,16 @@
         <v>1</v>
       </c>
       <c r="K274" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L274" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="M274" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="N274" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="O274" s="3" t="s">
         <v>477</v>
@@ -19839,16 +19839,16 @@
         <v>2</v>
       </c>
       <c r="K275" s="4" t="s">
-        <v>311</v>
+        <v>385</v>
       </c>
       <c r="L275" s="4" t="s">
-        <v>312</v>
+        <v>386</v>
       </c>
       <c r="M275" s="4" t="s">
-        <v>311</v>
+        <v>385</v>
       </c>
       <c r="N275" s="4" t="s">
-        <v>312</v>
+        <v>386</v>
       </c>
       <c r="O275" s="4" t="s">
         <v>480</v>
@@ -19886,16 +19886,16 @@
         <v>2</v>
       </c>
       <c r="K276" s="3" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="L276" s="3" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="M276" s="3" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="N276" s="3" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="O276" s="3" t="s">
         <v>60</v>
@@ -19933,16 +19933,16 @@
         <v>3</v>
       </c>
       <c r="K277" s="4" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="L277" s="4" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="M277" s="4" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="N277" s="4" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="O277" s="4" t="s">
         <v>60</v>
@@ -19980,16 +19980,16 @@
         <v>3</v>
       </c>
       <c r="K278" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="L278" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="M278" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="N278" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="O278" s="3" t="s">
         <v>60</v>
@@ -20027,16 +20027,16 @@
         <v>3</v>
       </c>
       <c r="K279" s="4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="L279" s="4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="M279" s="4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="N279" s="4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="O279" s="4" t="s">
         <v>60</v>
@@ -20074,16 +20074,16 @@
         <v>1</v>
       </c>
       <c r="K280" s="3" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="L280" s="3" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="M280" s="3" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="N280" s="3" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="O280" s="3" t="s">
         <v>60</v>
@@ -20121,16 +20121,16 @@
         <v>2</v>
       </c>
       <c r="K281" s="4" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="L281" s="4" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="M281" s="4" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="N281" s="4" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="O281" s="4" t="s">
         <v>474</v>
@@ -20215,16 +20215,16 @@
         <v>3</v>
       </c>
       <c r="K283" s="4" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="L283" s="4" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="M283" s="4" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="N283" s="4" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="O283" s="4" t="s">
         <v>60</v>
@@ -20262,16 +20262,16 @@
         <v>1</v>
       </c>
       <c r="K284" s="3" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="L284" s="3" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="M284" s="3" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="N284" s="3" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="O284" s="3" t="s">
         <v>60</v>
@@ -20497,16 +20497,16 @@
         <v>1</v>
       </c>
       <c r="K289" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L289" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="M289" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="N289" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="O289" s="4" t="s">
         <v>477</v>
@@ -20732,16 +20732,16 @@
         <v>3</v>
       </c>
       <c r="K294" s="3" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="L294" s="3" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="M294" s="3" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="N294" s="3" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="O294" s="3" t="s">
         <v>60</v>
@@ -20779,16 +20779,16 @@
         <v>3</v>
       </c>
       <c r="K295" s="4" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="L295" s="4" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="M295" s="4" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="N295" s="4" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="O295" s="4" t="s">
         <v>60</v>
@@ -20826,16 +20826,16 @@
         <v>3</v>
       </c>
       <c r="K296" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L296" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M296" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="N296" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="O296" s="3" t="s">
         <v>60</v>
@@ -20873,16 +20873,16 @@
         <v>1</v>
       </c>
       <c r="K297" s="4" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="L297" s="4" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="M297" s="4" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="N297" s="4" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="O297" s="4" t="s">
         <v>60</v>
@@ -20920,16 +20920,16 @@
         <v>2</v>
       </c>
       <c r="K298" s="3" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="L298" s="3" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="M298" s="3" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="N298" s="3" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="O298" s="3" t="s">
         <v>474</v>
@@ -20967,16 +20967,16 @@
         <v>1</v>
       </c>
       <c r="K299" s="4" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="L299" s="4" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="M299" s="4" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="N299" s="4" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="O299" s="4" t="s">
         <v>474</v>
@@ -21014,16 +21014,16 @@
         <v>3</v>
       </c>
       <c r="K300" s="3" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="L300" s="3" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="M300" s="3" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="N300" s="3" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="O300" s="3" t="s">
         <v>60</v>
@@ -21061,16 +21061,16 @@
         <v>1</v>
       </c>
       <c r="K301" s="4" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="L301" s="4" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="M301" s="4" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="N301" s="4" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="O301" s="4" t="s">
         <v>60</v>
@@ -21202,16 +21202,16 @@
         <v>3</v>
       </c>
       <c r="K304" s="3" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="L304" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="M304" s="3" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="N304" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="O304" s="3" t="s">
         <v>60</v>
@@ -21343,16 +21343,16 @@
         <v>1</v>
       </c>
       <c r="K307" s="4" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="L307" s="4" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="M307" s="4" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="N307" s="4" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="O307" s="4" t="s">
         <v>477</v>
@@ -21390,16 +21390,16 @@
         <v>2</v>
       </c>
       <c r="K308" s="3" t="s">
-        <v>314</v>
+        <v>385</v>
       </c>
       <c r="L308" s="3" t="s">
-        <v>315</v>
+        <v>386</v>
       </c>
       <c r="M308" s="3" t="s">
-        <v>314</v>
+        <v>385</v>
       </c>
       <c r="N308" s="3" t="s">
-        <v>315</v>
+        <v>386</v>
       </c>
       <c r="O308" s="3" t="s">
         <v>480</v>
@@ -21437,16 +21437,16 @@
         <v>3</v>
       </c>
       <c r="K309" s="4" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="L309" s="4" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="M309" s="4" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="N309" s="4" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="O309" s="4" t="s">
         <v>60</v>
@@ -21484,16 +21484,16 @@
         <v>3</v>
       </c>
       <c r="K310" s="3" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="L310" s="3" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="M310" s="3" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="N310" s="3" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="O310" s="3" t="s">
         <v>60</v>
@@ -21531,16 +21531,16 @@
         <v>3</v>
       </c>
       <c r="K311" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="L311" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="M311" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="N311" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="O311" s="4" t="s">
         <v>60</v>
@@ -21578,16 +21578,16 @@
         <v>1</v>
       </c>
       <c r="K312" s="3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="L312" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="M312" s="3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="N312" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="O312" s="3" t="s">
         <v>60</v>
@@ -21672,16 +21672,16 @@
         <v>1</v>
       </c>
       <c r="K314" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L314" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="M314" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="N314" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="O314" s="3" t="s">
         <v>474</v>
@@ -21719,16 +21719,16 @@
         <v>3</v>
       </c>
       <c r="K315" s="4" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="L315" s="4" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="M315" s="4" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="N315" s="4" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="O315" s="4" t="s">
         <v>60</v>
@@ -21907,16 +21907,16 @@
         <v>3</v>
       </c>
       <c r="K319" s="4" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="L319" s="4" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="M319" s="4" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="N319" s="4" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="O319" s="4" t="s">
         <v>60</v>
@@ -21954,16 +21954,16 @@
         <v>3</v>
       </c>
       <c r="K320" s="3" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="L320" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="M320" s="3" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="N320" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="O320" s="3" t="s">
         <v>60</v>
@@ -22001,16 +22001,16 @@
         <v>2</v>
       </c>
       <c r="K321" s="4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="L321" s="4" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="M321" s="4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="N321" s="4" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="O321" s="4" t="s">
         <v>60</v>
@@ -22048,16 +22048,16 @@
         <v>1</v>
       </c>
       <c r="K322" s="3" t="s">
-        <v>385</v>
+        <v>311</v>
       </c>
       <c r="L322" s="3" t="s">
-        <v>386</v>
+        <v>312</v>
       </c>
       <c r="M322" s="3" t="s">
-        <v>385</v>
+        <v>311</v>
       </c>
       <c r="N322" s="3" t="s">
-        <v>386</v>
+        <v>312</v>
       </c>
       <c r="O322" s="3" t="s">
         <v>477</v>
@@ -22095,16 +22095,16 @@
         <v>2</v>
       </c>
       <c r="K323" s="4" t="s">
-        <v>317</v>
+        <v>385</v>
       </c>
       <c r="L323" s="4" t="s">
-        <v>318</v>
+        <v>386</v>
       </c>
       <c r="M323" s="4" t="s">
-        <v>317</v>
+        <v>385</v>
       </c>
       <c r="N323" s="4" t="s">
-        <v>318</v>
+        <v>386</v>
       </c>
       <c r="O323" s="4" t="s">
         <v>480</v>
@@ -22142,16 +22142,16 @@
         <v>3</v>
       </c>
       <c r="K324" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L324" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M324" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="N324" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O324" s="3" t="s">
         <v>60</v>
@@ -22236,16 +22236,16 @@
         <v>3</v>
       </c>
       <c r="K326" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="L326" s="3" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="M326" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="N326" s="3" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="O326" s="3" t="s">
         <v>60</v>
@@ -22377,16 +22377,16 @@
         <v>1</v>
       </c>
       <c r="K329" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L329" s="4" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="M329" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="N329" s="4" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="O329" s="4" t="s">
         <v>474</v>
@@ -22424,16 +22424,16 @@
         <v>3</v>
       </c>
       <c r="K330" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="L330" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="M330" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="N330" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="O330" s="3" t="s">
         <v>60</v>
@@ -22471,16 +22471,16 @@
         <v>1</v>
       </c>
       <c r="K331" s="4" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="L331" s="4" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="M331" s="4" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="N331" s="4" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="O331" s="4" t="s">
         <v>60</v>
@@ -22612,16 +22612,16 @@
         <v>1</v>
       </c>
       <c r="K334" s="3" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="L334" s="3" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="M334" s="3" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="N334" s="3" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="O334" s="3" t="s">
         <v>477</v>
@@ -22706,16 +22706,16 @@
         <v>1</v>
       </c>
       <c r="K336" s="3" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="L336" s="3" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="M336" s="3" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="N336" s="3" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="O336" s="3" t="s">
         <v>477</v>
@@ -22753,16 +22753,16 @@
         <v>2</v>
       </c>
       <c r="K337" s="4" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="L337" s="4" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="M337" s="4" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="N337" s="4" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="O337" s="4" t="s">
         <v>480</v>
@@ -22800,16 +22800,16 @@
         <v>1</v>
       </c>
       <c r="K338" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="L338" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="M338" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="N338" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="O338" s="3" t="s">
         <v>477</v>
@@ -22847,16 +22847,16 @@
         <v>2</v>
       </c>
       <c r="K339" s="4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="L339" s="4" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="M339" s="4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="N339" s="4" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="O339" s="4" t="s">
         <v>480</v>
@@ -22894,16 +22894,16 @@
         <v>1</v>
       </c>
       <c r="K340" s="3" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="L340" s="3" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="M340" s="3" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="N340" s="3" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="O340" s="3" t="s">
         <v>477</v>
@@ -22941,16 +22941,16 @@
         <v>1</v>
       </c>
       <c r="K341" s="4" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="L341" s="4" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="M341" s="4" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="N341" s="4" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="O341" s="4" t="s">
         <v>480</v>
@@ -22988,16 +22988,16 @@
         <v>3</v>
       </c>
       <c r="K342" s="3" t="s">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="L342" s="3" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="M342" s="3" t="s">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="N342" s="3" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="O342" s="3" t="s">
         <v>60</v>
@@ -23082,16 +23082,16 @@
         <v>3</v>
       </c>
       <c r="K344" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="L344" s="3" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="M344" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="N344" s="3" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="O344" s="3" t="s">
         <v>60</v>
@@ -23129,16 +23129,16 @@
         <v>1</v>
       </c>
       <c r="K345" s="4" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="L345" s="4" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="M345" s="4" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="N345" s="4" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="O345" s="4" t="s">
         <v>60</v>
@@ -23176,16 +23176,16 @@
         <v>2</v>
       </c>
       <c r="K346" s="3" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="L346" s="3" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="M346" s="3" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="N346" s="3" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="O346" s="3" t="s">
         <v>474</v>
@@ -23223,16 +23223,16 @@
         <v>1</v>
       </c>
       <c r="K347" s="4" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="L347" s="4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="M347" s="4" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="N347" s="4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="O347" s="4" t="s">
         <v>474</v>
@@ -23270,16 +23270,16 @@
         <v>3</v>
       </c>
       <c r="K348" s="3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L348" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="M348" s="3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="N348" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="O348" s="3" t="s">
         <v>60</v>
@@ -23317,16 +23317,16 @@
         <v>1</v>
       </c>
       <c r="K349" s="4" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="L349" s="4" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="M349" s="4" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="N349" s="4" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="O349" s="4" t="s">
         <v>60</v>
@@ -23458,16 +23458,16 @@
         <v>1</v>
       </c>
       <c r="K352" s="3" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L352" s="3" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M352" s="3" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="N352" s="3" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="O352" s="3" t="s">
         <v>477</v>
@@ -23505,16 +23505,16 @@
         <v>2</v>
       </c>
       <c r="K353" s="4" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="L353" s="4" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="M353" s="4" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="N353" s="4" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="O353" s="4" t="s">
         <v>480</v>
@@ -23599,16 +23599,16 @@
         <v>2</v>
       </c>
       <c r="K355" s="4" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="L355" s="4" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="M355" s="4" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="N355" s="4" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="O355" s="4" t="s">
         <v>480</v>
@@ -23740,16 +23740,16 @@
         <v>1</v>
       </c>
       <c r="K358" s="3" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="L358" s="3" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="M358" s="3" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="N358" s="3" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="O358" s="3" t="s">
         <v>477</v>
@@ -23787,16 +23787,16 @@
         <v>1</v>
       </c>
       <c r="K359" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="L359" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="M359" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="N359" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="O359" s="4" t="s">
         <v>480</v>
@@ -23834,16 +23834,16 @@
         <v>3</v>
       </c>
       <c r="K360" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L360" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="M360" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N360" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="O360" s="3" t="s">
         <v>60</v>
@@ -23881,16 +23881,16 @@
         <v>3</v>
       </c>
       <c r="K361" s="4" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="L361" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="M361" s="4" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="N361" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="O361" s="4" t="s">
         <v>60</v>
@@ -23928,16 +23928,16 @@
         <v>3</v>
       </c>
       <c r="K362" s="3" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="L362" s="3" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="M362" s="3" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="N362" s="3" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="O362" s="3" t="s">
         <v>60</v>
@@ -24022,16 +24022,16 @@
         <v>2</v>
       </c>
       <c r="K364" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="L364" s="3" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="M364" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="N364" s="3" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="O364" s="3" t="s">
         <v>474</v>
@@ -24116,16 +24116,16 @@
         <v>3</v>
       </c>
       <c r="K366" s="3" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="L366" s="3" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="M366" s="3" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="N366" s="3" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="O366" s="3" t="s">
         <v>60</v>
@@ -24163,16 +24163,16 @@
         <v>1</v>
       </c>
       <c r="K367" s="4" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="L367" s="4" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="M367" s="4" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="N367" s="4" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="O367" s="4" t="s">
         <v>60</v>
@@ -24304,16 +24304,16 @@
         <v>1</v>
       </c>
       <c r="K370" s="3" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="L370" s="3" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="M370" s="3" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="N370" s="3" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="O370" s="3" t="s">
         <v>477</v>
@@ -24351,16 +24351,16 @@
         <v>2</v>
       </c>
       <c r="K371" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="L371" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="M371" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="N371" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="O371" s="4" t="s">
         <v>480</v>
@@ -24398,16 +24398,16 @@
         <v>1</v>
       </c>
       <c r="K372" s="3" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="L372" s="3" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="M372" s="3" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="N372" s="3" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="O372" s="3" t="s">
         <v>477</v>
@@ -24445,16 +24445,16 @@
         <v>2</v>
       </c>
       <c r="K373" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="L373" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="M373" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="N373" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="O373" s="4" t="s">
         <v>480</v>
@@ -24586,16 +24586,16 @@
         <v>1</v>
       </c>
       <c r="K376" s="3" t="s">
-        <v>385</v>
+        <v>314</v>
       </c>
       <c r="L376" s="3" t="s">
-        <v>386</v>
+        <v>315</v>
       </c>
       <c r="M376" s="3" t="s">
-        <v>385</v>
+        <v>314</v>
       </c>
       <c r="N376" s="3" t="s">
-        <v>386</v>
+        <v>315</v>
       </c>
       <c r="O376" s="3" t="s">
         <v>477</v>
@@ -24633,16 +24633,16 @@
         <v>1</v>
       </c>
       <c r="K377" s="4" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="L377" s="4" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="M377" s="4" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="N377" s="4" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="O377" s="4" t="s">
         <v>480</v>
@@ -24680,16 +24680,16 @@
         <v>3</v>
       </c>
       <c r="K378" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="L378" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="M378" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="N378" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="O378" s="3" t="s">
         <v>60</v>
@@ -24727,16 +24727,16 @@
         <v>3</v>
       </c>
       <c r="K379" s="4" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="L379" s="4" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="M379" s="4" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="N379" s="4" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="O379" s="4" t="s">
         <v>60</v>
@@ -24774,16 +24774,16 @@
         <v>3</v>
       </c>
       <c r="K380" s="3" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="L380" s="3" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="M380" s="3" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="N380" s="3" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="O380" s="3" t="s">
         <v>60</v>
@@ -24868,16 +24868,16 @@
         <v>2</v>
       </c>
       <c r="K382" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L382" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="M382" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="N382" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="O382" s="3" t="s">
         <v>474</v>
@@ -24962,16 +24962,16 @@
         <v>3</v>
       </c>
       <c r="K384" s="3" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="L384" s="3" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="M384" s="3" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="N384" s="3" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="O384" s="3" t="s">
         <v>60</v>
@@ -25009,16 +25009,16 @@
         <v>1</v>
       </c>
       <c r="K385" s="4" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="L385" s="4" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="M385" s="4" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="N385" s="4" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="O385" s="4" t="s">
         <v>60</v>
@@ -25150,16 +25150,16 @@
         <v>1</v>
       </c>
       <c r="K388" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="L388" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="M388" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N388" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="O388" s="3" t="s">
         <v>477</v>
@@ -25197,16 +25197,16 @@
         <v>2</v>
       </c>
       <c r="K389" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="L389" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="M389" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="N389" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="O389" s="4" t="s">
         <v>480</v>
@@ -25244,16 +25244,16 @@
         <v>1</v>
       </c>
       <c r="K390" s="3" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="L390" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="M390" s="3" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="N390" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="O390" s="3" t="s">
         <v>477</v>
@@ -25291,16 +25291,16 @@
         <v>2</v>
       </c>
       <c r="K391" s="4" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="L391" s="4" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="M391" s="4" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="N391" s="4" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="O391" s="4" t="s">
         <v>480</v>
@@ -25338,16 +25338,16 @@
         <v>1</v>
       </c>
       <c r="K392" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="L392" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="M392" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N392" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="O392" s="3" t="s">
         <v>477</v>
@@ -25385,16 +25385,16 @@
         <v>2</v>
       </c>
       <c r="K393" s="4" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="L393" s="4" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="M393" s="4" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N393" s="4" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="O393" s="4" t="s">
         <v>480</v>
@@ -25432,16 +25432,16 @@
         <v>1</v>
       </c>
       <c r="K394" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="L394" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="M394" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="N394" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="O394" s="3" t="s">
         <v>477</v>
@@ -25479,16 +25479,16 @@
         <v>1</v>
       </c>
       <c r="K395" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L395" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M395" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="N395" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="O395" s="4" t="s">
         <v>480</v>
@@ -25526,16 +25526,16 @@
         <v>3</v>
       </c>
       <c r="K396" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="L396" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="M396" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="N396" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="O396" s="3" t="s">
         <v>60</v>
@@ -25573,16 +25573,16 @@
         <v>3</v>
       </c>
       <c r="K397" s="4" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="L397" s="4" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="M397" s="4" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="N397" s="4" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="O397" s="4" t="s">
         <v>60</v>
@@ -25620,16 +25620,16 @@
         <v>3</v>
       </c>
       <c r="K398" s="3" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="L398" s="3" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="M398" s="3" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="N398" s="3" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="O398" s="3" t="s">
         <v>60</v>
@@ -25667,16 +25667,16 @@
         <v>1</v>
       </c>
       <c r="K399" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="L399" s="4" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="M399" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="N399" s="4" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="O399" s="4" t="s">
         <v>60</v>
@@ -25714,16 +25714,16 @@
         <v>2</v>
       </c>
       <c r="K400" s="3" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="L400" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="M400" s="3" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="N400" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="O400" s="3" t="s">
         <v>474</v>
@@ -25761,16 +25761,16 @@
         <v>1</v>
       </c>
       <c r="K401" s="4" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="L401" s="4" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="M401" s="4" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="N401" s="4" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="O401" s="4" t="s">
         <v>474</v>
@@ -25808,16 +25808,16 @@
         <v>3</v>
       </c>
       <c r="K402" s="3" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="L402" s="3" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="M402" s="3" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="N402" s="3" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="O402" s="3" t="s">
         <v>60</v>
@@ -25855,16 +25855,16 @@
         <v>1</v>
       </c>
       <c r="K403" s="4" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="L403" s="4" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="M403" s="4" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="N403" s="4" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="O403" s="4" t="s">
         <v>60</v>
@@ -25996,16 +25996,16 @@
         <v>1</v>
       </c>
       <c r="K406" s="3" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="L406" s="3" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="M406" s="3" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="N406" s="3" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="O406" s="3" t="s">
         <v>477</v>
@@ -26043,16 +26043,16 @@
         <v>2</v>
       </c>
       <c r="K407" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L407" s="4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="M407" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="N407" s="4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="O407" s="4" t="s">
         <v>480</v>
@@ -26090,16 +26090,16 @@
         <v>1</v>
       </c>
       <c r="K408" s="3" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="L408" s="3" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="M408" s="3" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="N408" s="3" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="O408" s="3" t="s">
         <v>477</v>
@@ -26137,16 +26137,16 @@
         <v>2</v>
       </c>
       <c r="K409" s="4" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="L409" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="M409" s="4" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="N409" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="O409" s="4" t="s">
         <v>480</v>
@@ -26184,16 +26184,16 @@
         <v>1</v>
       </c>
       <c r="K410" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="L410" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="M410" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="N410" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="O410" s="3" t="s">
         <v>477</v>
@@ -26231,16 +26231,16 @@
         <v>2</v>
       </c>
       <c r="K411" s="4" t="s">
-        <v>385</v>
+        <v>311</v>
       </c>
       <c r="L411" s="4" t="s">
-        <v>386</v>
+        <v>312</v>
       </c>
       <c r="M411" s="4" t="s">
-        <v>385</v>
+        <v>311</v>
       </c>
       <c r="N411" s="4" t="s">
-        <v>386</v>
+        <v>312</v>
       </c>
       <c r="O411" s="4" t="s">
         <v>480</v>
@@ -26278,16 +26278,16 @@
         <v>2</v>
       </c>
       <c r="K412" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L412" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="M412" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="N412" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="O412" s="3" t="s">
         <v>60</v>
@@ -26325,16 +26325,16 @@
         <v>3</v>
       </c>
       <c r="K413" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="L413" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="M413" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="N413" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="O413" s="4" t="s">
         <v>60</v>
@@ -26372,16 +26372,16 @@
         <v>3</v>
       </c>
       <c r="K414" s="3" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="L414" s="3" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="M414" s="3" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="N414" s="3" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="O414" s="3" t="s">
         <v>60</v>
@@ -26419,16 +26419,16 @@
         <v>3</v>
       </c>
       <c r="K415" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L415" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="M415" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="N415" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="O415" s="4" t="s">
         <v>60</v>
@@ -26466,16 +26466,16 @@
         <v>1</v>
       </c>
       <c r="K416" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="L416" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="M416" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="N416" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="O416" s="3" t="s">
         <v>60</v>
@@ -26513,16 +26513,16 @@
         <v>2</v>
       </c>
       <c r="K417" s="4" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="L417" s="4" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="M417" s="4" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="N417" s="4" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="O417" s="4" t="s">
         <v>474</v>
@@ -26560,16 +26560,16 @@
         <v>1</v>
       </c>
       <c r="K418" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="L418" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="M418" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="N418" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="O418" s="3" t="s">
         <v>474</v>
@@ -26607,16 +26607,16 @@
         <v>3</v>
       </c>
       <c r="K419" s="4" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="L419" s="4" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="M419" s="4" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="N419" s="4" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="O419" s="4" t="s">
         <v>60</v>
@@ -26654,16 +26654,16 @@
         <v>1</v>
       </c>
       <c r="K420" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="L420" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="M420" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="N420" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="O420" s="3" t="s">
         <v>60</v>
@@ -26795,16 +26795,16 @@
         <v>1</v>
       </c>
       <c r="K423" s="4" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="L423" s="4" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="M423" s="4" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="N423" s="4" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="O423" s="4" t="s">
         <v>477</v>
@@ -26842,16 +26842,16 @@
         <v>2</v>
       </c>
       <c r="K424" s="3" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="L424" s="3" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="M424" s="3" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="N424" s="3" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="O424" s="3" t="s">
         <v>480</v>
@@ -26889,16 +26889,16 @@
         <v>1</v>
       </c>
       <c r="K425" s="4" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="L425" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="M425" s="4" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="N425" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="O425" s="4" t="s">
         <v>477</v>
@@ -26936,16 +26936,16 @@
         <v>2</v>
       </c>
       <c r="K426" s="3" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="L426" s="3" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="M426" s="3" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="N426" s="3" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="O426" s="3" t="s">
         <v>480</v>
@@ -26983,16 +26983,16 @@
         <v>1</v>
       </c>
       <c r="K427" s="4" t="s">
-        <v>385</v>
+        <v>317</v>
       </c>
       <c r="L427" s="4" t="s">
-        <v>386</v>
+        <v>318</v>
       </c>
       <c r="M427" s="4" t="s">
-        <v>385</v>
+        <v>317</v>
       </c>
       <c r="N427" s="4" t="s">
-        <v>386</v>
+        <v>318</v>
       </c>
       <c r="O427" s="4" t="s">
         <v>477</v>
@@ -27030,16 +27030,16 @@
         <v>2</v>
       </c>
       <c r="K428" s="3" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="L428" s="3" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="M428" s="3" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="N428" s="3" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="O428" s="3" t="s">
         <v>480</v>
@@ -27077,16 +27077,16 @@
         <v>2</v>
       </c>
       <c r="K429" s="4" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="L429" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="M429" s="4" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="N429" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O429" s="4" t="s">
         <v>60</v>
@@ -27124,16 +27124,16 @@
         <v>3</v>
       </c>
       <c r="K430" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="L430" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="M430" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="N430" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="O430" s="3" t="s">
         <v>60</v>
@@ -27218,16 +27218,16 @@
         <v>3</v>
       </c>
       <c r="K432" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="L432" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="M432" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="N432" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="O432" s="3" t="s">
         <v>60</v>
@@ -27265,16 +27265,16 @@
         <v>1</v>
       </c>
       <c r="K433" s="4" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="L433" s="4" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="M433" s="4" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="N433" s="4" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="O433" s="4" t="s">
         <v>60</v>
@@ -27312,16 +27312,16 @@
         <v>2</v>
       </c>
       <c r="K434" s="3" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="L434" s="3" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="M434" s="3" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="N434" s="3" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="O434" s="3" t="s">
         <v>474</v>
@@ -27359,16 +27359,16 @@
         <v>1</v>
       </c>
       <c r="K435" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L435" s="4" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="M435" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="N435" s="4" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="O435" s="4" t="s">
         <v>474</v>
@@ -27406,16 +27406,16 @@
         <v>3</v>
       </c>
       <c r="K436" s="3" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="L436" s="3" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="M436" s="3" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="N436" s="3" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="O436" s="3" t="s">
         <v>60</v>
@@ -27453,16 +27453,16 @@
         <v>1</v>
       </c>
       <c r="K437" s="4" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="L437" s="4" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="M437" s="4" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="N437" s="4" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="O437" s="4" t="s">
         <v>60</v>
@@ -27688,16 +27688,16 @@
         <v>1</v>
       </c>
       <c r="K442" s="3" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="L442" s="3" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="M442" s="3" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="N442" s="3" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="O442" s="3" t="s">
         <v>477</v>
@@ -27782,16 +27782,16 @@
         <v>1</v>
       </c>
       <c r="K444" s="3" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="L444" s="3" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="M444" s="3" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="N444" s="3" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="O444" s="3" t="s">
         <v>477</v>
@@ -27829,16 +27829,16 @@
         <v>2</v>
       </c>
       <c r="K445" s="4" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="L445" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="M445" s="4" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="N445" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="O445" s="4" t="s">
         <v>480</v>
@@ -27923,16 +27923,16 @@
         <v>3</v>
       </c>
       <c r="K447" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L447" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="M447" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="N447" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O447" s="4" t="s">
         <v>60</v>
@@ -28017,16 +28017,16 @@
         <v>3</v>
       </c>
       <c r="K449" s="4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="L449" s="4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="M449" s="4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="N449" s="4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="O449" s="4" t="s">
         <v>60</v>
@@ -28064,16 +28064,16 @@
         <v>1</v>
       </c>
       <c r="K450" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="L450" s="3" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="M450" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="N450" s="3" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="O450" s="3" t="s">
         <v>60</v>
@@ -28111,16 +28111,16 @@
         <v>2</v>
       </c>
       <c r="K451" s="4" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="L451" s="4" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="M451" s="4" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="N451" s="4" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="O451" s="4" t="s">
         <v>474</v>
@@ -28158,16 +28158,16 @@
         <v>1</v>
       </c>
       <c r="K452" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="L452" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="M452" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="N452" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="O452" s="3" t="s">
         <v>474</v>
@@ -28205,16 +28205,16 @@
         <v>3</v>
       </c>
       <c r="K453" s="4" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="L453" s="4" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="M453" s="4" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="N453" s="4" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="O453" s="4" t="s">
         <v>60</v>
@@ -28252,16 +28252,16 @@
         <v>1</v>
       </c>
       <c r="K454" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L454" s="3" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="M454" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="N454" s="3" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="O454" s="3" t="s">
         <v>60</v>
@@ -28393,16 +28393,16 @@
         <v>3</v>
       </c>
       <c r="K457" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="L457" s="4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="M457" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="N457" s="4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="O457" s="4" t="s">
         <v>60</v>
@@ -28440,16 +28440,16 @@
         <v>3</v>
       </c>
       <c r="K458" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="L458" s="3" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M458" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="N458" s="3" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="O458" s="3" t="s">
         <v>60</v>
@@ -28487,16 +28487,16 @@
         <v>2</v>
       </c>
       <c r="K459" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="L459" s="4" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="M459" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="N459" s="4" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="O459" s="4" t="s">
         <v>60</v>
@@ -28581,16 +28581,16 @@
         <v>2</v>
       </c>
       <c r="K461" s="4" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="L461" s="4" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="M461" s="4" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="N461" s="4" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="O461" s="4" t="s">
         <v>480</v>
@@ -28628,16 +28628,16 @@
         <v>3</v>
       </c>
       <c r="K462" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L462" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="M462" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="N462" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="O462" s="3" t="s">
         <v>60</v>
@@ -28722,16 +28722,16 @@
         <v>3</v>
       </c>
       <c r="K464" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="L464" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="M464" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="N464" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="O464" s="3" t="s">
         <v>60</v>
@@ -28769,16 +28769,16 @@
         <v>1</v>
       </c>
       <c r="K465" s="4" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="L465" s="4" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="M465" s="4" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="N465" s="4" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="O465" s="4" t="s">
         <v>60</v>
@@ -28816,16 +28816,16 @@
         <v>2</v>
       </c>
       <c r="K466" s="3" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="L466" s="3" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="M466" s="3" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="N466" s="3" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="O466" s="3" t="s">
         <v>474</v>
@@ -28910,16 +28910,16 @@
         <v>3</v>
       </c>
       <c r="K468" s="3" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="L468" s="3" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="M468" s="3" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="N468" s="3" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="O468" s="3" t="s">
         <v>60</v>
@@ -28957,16 +28957,16 @@
         <v>1</v>
       </c>
       <c r="K469" s="4" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L469" s="4" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="M469" s="4" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="N469" s="4" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="O469" s="4" t="s">
         <v>60</v>
@@ -29098,16 +29098,16 @@
         <v>3</v>
       </c>
       <c r="K472" s="3" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="L472" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="M472" s="3" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="N472" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="O472" s="3" t="s">
         <v>60</v>
@@ -29286,16 +29286,16 @@
         <v>2</v>
       </c>
       <c r="K476" s="3" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="L476" s="3" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="M476" s="3" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="N476" s="3" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="O476" s="3" t="s">
         <v>480</v>
@@ -29333,16 +29333,16 @@
         <v>3</v>
       </c>
       <c r="K477" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="L477" s="4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="M477" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="N477" s="4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="O477" s="4" t="s">
         <v>60</v>
@@ -29427,16 +29427,16 @@
         <v>3</v>
       </c>
       <c r="K479" s="4" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L479" s="4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M479" s="4" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="N479" s="4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="O479" s="4" t="s">
         <v>60</v>
@@ -29521,16 +29521,16 @@
         <v>2</v>
       </c>
       <c r="K481" s="4" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="L481" s="4" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="M481" s="4" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="N481" s="4" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="O481" s="4" t="s">
         <v>474</v>
@@ -29615,16 +29615,16 @@
         <v>3</v>
       </c>
       <c r="K483" s="4" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="L483" s="4" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="M483" s="4" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="N483" s="4" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="O483" s="4" t="s">
         <v>60</v>
@@ -29662,16 +29662,16 @@
         <v>1</v>
       </c>
       <c r="K484" s="3" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="L484" s="3" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M484" s="3" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="N484" s="3" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="O484" s="3" t="s">
         <v>60</v>
@@ -29803,16 +29803,16 @@
         <v>3</v>
       </c>
       <c r="K487" s="4" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="L487" s="4" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="M487" s="4" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="N487" s="4" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="O487" s="4" t="s">
         <v>60</v>
@@ -29991,16 +29991,16 @@
         <v>2</v>
       </c>
       <c r="K491" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="L491" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="M491" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="N491" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="O491" s="4" t="s">
         <v>480</v>
@@ -30038,16 +30038,16 @@
         <v>3</v>
       </c>
       <c r="K492" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L492" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M492" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="N492" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O492" s="3" t="s">
         <v>60</v>
@@ -30085,16 +30085,16 @@
         <v>3</v>
       </c>
       <c r="K493" s="4" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="L493" s="4" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="M493" s="4" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="N493" s="4" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="O493" s="4" t="s">
         <v>60</v>
@@ -30132,16 +30132,16 @@
         <v>3</v>
       </c>
       <c r="K494" s="3" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="L494" s="3" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="M494" s="3" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="N494" s="3" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="O494" s="3" t="s">
         <v>60</v>
@@ -30179,16 +30179,16 @@
         <v>1</v>
       </c>
       <c r="K495" s="4" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="L495" s="4" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="M495" s="4" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="N495" s="4" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="O495" s="4" t="s">
         <v>60</v>
@@ -30226,16 +30226,16 @@
         <v>2</v>
       </c>
       <c r="K496" s="3" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="L496" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="M496" s="3" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="N496" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="O496" s="3" t="s">
         <v>474</v>
@@ -30273,16 +30273,16 @@
         <v>1</v>
       </c>
       <c r="K497" s="4" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="L497" s="4" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="M497" s="4" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="N497" s="4" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="O497" s="4" t="s">
         <v>474</v>
@@ -30320,16 +30320,16 @@
         <v>3</v>
       </c>
       <c r="K498" s="3" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="L498" s="3" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="M498" s="3" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="N498" s="3" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="O498" s="3" t="s">
         <v>60</v>
@@ -30367,16 +30367,16 @@
         <v>1</v>
       </c>
       <c r="K499" s="4" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="L499" s="4" t="s">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="M499" s="4" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="N499" s="4" t="s">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="O499" s="4" t="s">
         <v>60</v>
@@ -30508,16 +30508,16 @@
         <v>1</v>
       </c>
       <c r="K502" s="3" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="L502" s="3" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="M502" s="3" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="N502" s="3" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="O502" s="3" t="s">
         <v>477</v>
@@ -30602,16 +30602,16 @@
         <v>1</v>
       </c>
       <c r="K504" s="3" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="L504" s="3" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="M504" s="3" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="N504" s="3" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="O504" s="3" t="s">
         <v>477</v>
@@ -30649,16 +30649,16 @@
         <v>2</v>
       </c>
       <c r="K505" s="4" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="L505" s="4" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="M505" s="4" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="N505" s="4" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="O505" s="4" t="s">
         <v>480</v>
@@ -30696,16 +30696,16 @@
         <v>2</v>
       </c>
       <c r="K506" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="L506" s="3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="M506" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="N506" s="3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="O506" s="3" t="s">
         <v>60</v>
@@ -30790,16 +30790,16 @@
         <v>2</v>
       </c>
       <c r="K508" s="3" t="s">
-        <v>385</v>
+        <v>314</v>
       </c>
       <c r="L508" s="3" t="s">
-        <v>386</v>
+        <v>315</v>
       </c>
       <c r="M508" s="3" t="s">
-        <v>385</v>
+        <v>314</v>
       </c>
       <c r="N508" s="3" t="s">
-        <v>386</v>
+        <v>315</v>
       </c>
       <c r="O508" s="3" t="s">
         <v>480</v>
